--- a/docs/photo-triage.xlsx
+++ b/docs/photo-triage.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Triage'!$A$1:$N$244</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Triage'!$A$1:$O$244</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -6603,7 +6603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N244"/>
+  <dimension ref="A1:O244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -6617,9 +6617,10 @@
     <col width="48" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -6680,15 +6681,20 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Client clearance (batch 2)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Duplicate of</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Project # (see projects-inventory.xlsx)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Original file name</t>
         </is>
@@ -6737,8 +6743,9 @@
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="6" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="6" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0094.jpg</t>
         </is>
@@ -6790,13 +6797,14 @@
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>photo-001</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0094_1.jpg</t>
         </is>
@@ -6845,8 +6853,9 @@
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="6" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0095.jpg</t>
         </is>
@@ -6898,13 +6907,14 @@
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>photo-003</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0095_1.jpg</t>
         </is>
@@ -6957,8 +6967,9 @@
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="6" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0096.jpg</t>
         </is>
@@ -7010,13 +7021,14 @@
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>photo-005</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" s="6" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0096_1.jpg</t>
         </is>
@@ -7069,8 +7081,9 @@
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="6" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="6" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0097.jpg</t>
         </is>
@@ -7126,13 +7139,14 @@
           <t>Public-building sign/emblem</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>photo-007</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="6" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0097_1.jpg</t>
         </is>
@@ -7188,9 +7202,14 @@
           <t>Public-building sign</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="6" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>POLICE SITE — not published; asked again 2026-09-16. faces — publishing permission granted 2026-09-16</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="6" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0098.jpg</t>
         </is>
@@ -7248,11 +7267,16 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>POLICE SITE — not published; asked again 2026-09-16. faces — publishing permission granted 2026-09-16</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
           <t>photo-009</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N11" s="6" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0098_1.jpg</t>
         </is>
@@ -7305,8 +7329,9 @@
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="6" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="6" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0099.jpg</t>
         </is>
@@ -7355,8 +7380,9 @@
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="6" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="6" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0100.jpg</t>
         </is>
@@ -7408,13 +7434,14 @@
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>photo-012</t>
         </is>
       </c>
-      <c r="M14" s="6" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N14" s="6" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0100_1.jpg</t>
         </is>
@@ -7463,8 +7490,9 @@
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="6" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="6" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0101.jpg</t>
         </is>
@@ -7513,8 +7541,9 @@
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="6" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="6" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0102.jpg</t>
         </is>
@@ -7566,13 +7595,14 @@
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>photo-015</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N17" s="6" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0102_1.jpg</t>
         </is>
@@ -7629,8 +7659,9 @@
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="6" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="6" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0103.jpg</t>
         </is>
@@ -7683,8 +7714,9 @@
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="6" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="6" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0104.jpg</t>
         </is>
@@ -7736,13 +7768,14 @@
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>photo-018</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N20" s="6" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0104_1.jpg</t>
         </is>
@@ -7795,8 +7828,9 @@
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="6" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="6" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0105.jpg</t>
         </is>
@@ -7848,13 +7882,14 @@
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>photo-020</t>
         </is>
       </c>
-      <c r="M22" s="6" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N22" s="6" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0105_1.jpg</t>
         </is>
@@ -7907,8 +7942,9 @@
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="6" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0107.jpg</t>
         </is>
@@ -7960,13 +7996,14 @@
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>photo-022</t>
         </is>
       </c>
-      <c r="M24" s="6" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N24" s="6" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0107_1.jpg</t>
         </is>
@@ -8019,8 +8056,9 @@
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="6" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="6" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0108.jpg</t>
         </is>
@@ -8072,13 +8110,14 @@
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>photo-024</t>
         </is>
       </c>
-      <c r="M26" s="6" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N26" s="6" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0108_1.jpg</t>
         </is>
@@ -8131,8 +8170,9 @@
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="6" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="6" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0109.jpg</t>
         </is>
@@ -8184,13 +8224,14 @@
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>photo-026</t>
         </is>
       </c>
-      <c r="M28" s="6" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N28" s="6" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0109_1.jpg</t>
         </is>
@@ -8239,8 +8280,9 @@
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="6" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="6" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0110.jpg</t>
         </is>
@@ -8292,13 +8334,14 @@
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>photo-028</t>
         </is>
       </c>
-      <c r="M30" s="6" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N30" s="6" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0110_1.jpg</t>
         </is>
@@ -8351,8 +8394,9 @@
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="6" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="6" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0111.jpg</t>
         </is>
@@ -8404,13 +8448,14 @@
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>photo-030</t>
         </is>
       </c>
-      <c r="M32" s="6" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N32" s="6" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0111_1.jpg</t>
         </is>
@@ -8463,8 +8508,9 @@
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="6" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="6" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0112.jpg</t>
         </is>
@@ -8516,13 +8562,14 @@
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>photo-032</t>
         </is>
       </c>
-      <c r="M34" s="6" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="N34" s="6" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0112_1.jpg</t>
         </is>
@@ -8578,9 +8625,14 @@
           <t>Building sign</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="6" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>POLICE SITE — not published; asked again 2026-09-16. faces — publishing permission granted 2026-09-16</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="6" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0113.jpg</t>
         </is>
@@ -8638,11 +8690,16 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
+          <t>POLICE SITE — not published; asked again 2026-09-16. faces — publishing permission granted 2026-09-16</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
           <t>photo-034</t>
         </is>
       </c>
-      <c r="M36" s="6" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="N36" s="6" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0113_1.jpg</t>
         </is>
@@ -8691,8 +8748,9 @@
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="6" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="6" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0114.jpg</t>
         </is>
@@ -8744,13 +8802,14 @@
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>photo-036</t>
         </is>
       </c>
-      <c r="M38" s="6" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="N38" s="6" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0114_1.jpg</t>
         </is>
@@ -8799,8 +8858,9 @@
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="6" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="6" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0115.jpg</t>
         </is>
@@ -8853,8 +8913,9 @@
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="6" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="6" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0116.jpg</t>
         </is>
@@ -8906,13 +8967,14 @@
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>photo-039</t>
         </is>
       </c>
-      <c r="M41" s="6" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="N41" s="6" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0116_1.jpg</t>
         </is>
@@ -8965,8 +9027,9 @@
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="6" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="6" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0117.jpg</t>
         </is>
@@ -9018,13 +9081,14 @@
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>photo-041</t>
         </is>
       </c>
-      <c r="M43" s="6" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="N43" s="6" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0117_1.jpg</t>
         </is>
@@ -9076,9 +9140,14 @@
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="6" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>POLICE SITE — not published; asked again 2026-09-16. faces — publishing permission granted 2026-09-16</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="6" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0118.jpg</t>
         </is>
@@ -9132,11 +9201,16 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
+          <t>POLICE SITE — not published; asked again 2026-09-16. faces — publishing permission granted 2026-09-16</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
           <t>photo-043</t>
         </is>
       </c>
-      <c r="M45" s="6" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="N45" s="6" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0118_1.jpg</t>
         </is>
@@ -9185,8 +9259,9 @@
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="6" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="6" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0119.jpg</t>
         </is>
@@ -9238,13 +9313,14 @@
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
         <is>
           <t>photo-045</t>
         </is>
       </c>
-      <c r="M47" s="6" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="N47" s="6" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0119_1.jpg</t>
         </is>
@@ -9301,8 +9377,9 @@
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="6" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="6" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0120.jpg</t>
         </is>
@@ -9358,13 +9435,14 @@
           <t>Police building and vehicles</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>photo-047</t>
         </is>
       </c>
-      <c r="M49" s="6" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="N49" s="6" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0120_1.jpg</t>
         </is>
@@ -9417,8 +9495,9 @@
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="6" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="6" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0121.jpg</t>
         </is>
@@ -9470,13 +9549,14 @@
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>photo-049</t>
         </is>
       </c>
-      <c r="M51" s="6" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="N51" s="6" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0121_1.jpg</t>
         </is>
@@ -9525,8 +9605,9 @@
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="6" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="6" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0122.jpg</t>
         </is>
@@ -9579,8 +9660,9 @@
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="6" t="inlineStr"/>
-      <c r="N53" s="2" t="inlineStr">
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="6" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0123.jpg</t>
         </is>
@@ -9632,13 +9714,14 @@
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>photo-052</t>
         </is>
       </c>
-      <c r="M54" s="6" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="N54" s="6" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0123_1.jpg</t>
         </is>
@@ -9695,8 +9778,9 @@
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="6" t="inlineStr"/>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="6" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0124.jpg</t>
         </is>
@@ -9752,13 +9836,14 @@
           <t>Police building sign</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>photo-054</t>
         </is>
       </c>
-      <c r="M56" s="6" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="N56" s="6" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0124_1.jpg</t>
         </is>
@@ -9815,8 +9900,9 @@
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="6" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr">
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="6" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0125.jpg</t>
         </is>
@@ -9872,13 +9958,14 @@
           <t>Barriers marked POLICE</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
         <is>
           <t>photo-056</t>
         </is>
       </c>
-      <c r="M58" s="6" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="N58" s="6" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0125_1.jpg</t>
         </is>
@@ -9931,8 +10018,9 @@
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="6" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr">
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="6" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0126.jpg</t>
         </is>
@@ -9984,13 +10072,14 @@
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>photo-058</t>
         </is>
       </c>
-      <c r="M60" s="6" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr">
+      <c r="N60" s="6" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0126_1.jpg</t>
         </is>
@@ -10047,8 +10136,9 @@
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="6" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr">
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="6" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0127.jpg</t>
         </is>
@@ -10104,13 +10194,14 @@
           <t>Security barriers</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
         <is>
           <t>photo-060</t>
         </is>
       </c>
-      <c r="M62" s="6" t="inlineStr"/>
-      <c r="N62" s="2" t="inlineStr">
+      <c r="N62" s="6" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0127_1.jpg</t>
         </is>
@@ -10167,8 +10258,9 @@
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="6" t="inlineStr"/>
-      <c r="N63" s="2" t="inlineStr">
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="6" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0128.jpg</t>
         </is>
@@ -10224,13 +10316,14 @@
           <t>Guard tower</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>photo-062</t>
         </is>
       </c>
-      <c r="M64" s="6" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr">
+      <c r="N64" s="6" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0128_1.jpg</t>
         </is>
@@ -10287,8 +10380,9 @@
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr"/>
-      <c r="M65" s="6" t="inlineStr"/>
-      <c r="N65" s="2" t="inlineStr">
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="6" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0129.jpg</t>
         </is>
@@ -10344,13 +10438,14 @@
           <t>Barriers marked POLICE</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
         <is>
           <t>photo-064</t>
         </is>
       </c>
-      <c r="M66" s="6" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr">
+      <c r="N66" s="6" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0129_1.jpg</t>
         </is>
@@ -10399,8 +10494,9 @@
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
-      <c r="M67" s="6" t="inlineStr"/>
-      <c r="N67" s="2" t="inlineStr">
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="6" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0130.jpg</t>
         </is>
@@ -10452,13 +10548,14 @@
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
         <is>
           <t>photo-066</t>
         </is>
       </c>
-      <c r="M68" s="6" t="inlineStr"/>
-      <c r="N68" s="2" t="inlineStr">
+      <c r="N68" s="6" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0130_1.jpg</t>
         </is>
@@ -10511,8 +10608,9 @@
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
-      <c r="M69" s="6" t="inlineStr"/>
-      <c r="N69" s="2" t="inlineStr">
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="6" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0131.jpg</t>
         </is>
@@ -10564,13 +10662,14 @@
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr">
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
         <is>
           <t>photo-068</t>
         </is>
       </c>
-      <c r="M70" s="6" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr">
+      <c r="N70" s="6" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0131_1.jpg</t>
         </is>
@@ -10627,8 +10726,9 @@
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="6" t="inlineStr"/>
-      <c r="N71" s="2" t="inlineStr">
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="6" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0132.jpg</t>
         </is>
@@ -10684,13 +10784,14 @@
           <t>Security barriers</t>
         </is>
       </c>
-      <c r="L72" s="2" t="inlineStr">
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
         <is>
           <t>photo-070</t>
         </is>
       </c>
-      <c r="M72" s="6" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr">
+      <c r="N72" s="6" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0132_1.jpg</t>
         </is>
@@ -10747,8 +10848,9 @@
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="6" t="inlineStr"/>
-      <c r="N73" s="2" t="inlineStr">
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="6" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0133.jpg</t>
         </is>
@@ -10804,13 +10906,14 @@
           <t>Truck decals</t>
         </is>
       </c>
-      <c r="L74" s="2" t="inlineStr">
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
         <is>
           <t>photo-072</t>
         </is>
       </c>
-      <c r="M74" s="6" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr">
+      <c r="N74" s="6" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0133_1.jpg</t>
         </is>
@@ -10859,8 +10962,9 @@
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
-      <c r="M75" s="6" t="inlineStr"/>
-      <c r="N75" s="2" t="inlineStr">
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="6" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0134.jpg</t>
         </is>
@@ -10912,13 +11016,14 @@
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr">
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
         <is>
           <t>photo-074</t>
         </is>
       </c>
-      <c r="M76" s="6" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr">
+      <c r="N76" s="6" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0134_1.jpg</t>
         </is>
@@ -10967,8 +11072,9 @@
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
-      <c r="M77" s="6" t="inlineStr"/>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="6" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0135.jpg</t>
         </is>
@@ -11021,8 +11127,9 @@
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="6" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr">
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="6" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0136.jpg</t>
         </is>
@@ -11074,13 +11181,14 @@
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr">
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
         <is>
           <t>photo-077</t>
         </is>
       </c>
-      <c r="M79" s="6" t="inlineStr"/>
-      <c r="N79" s="2" t="inlineStr">
+      <c r="N79" s="6" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0136_1.jpg</t>
         </is>
@@ -11137,8 +11245,9 @@
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="6" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr">
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="6" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0137.jpg</t>
         </is>
@@ -11194,13 +11303,14 @@
           <t>Third-party brand (FOX) on a truck</t>
         </is>
       </c>
-      <c r="L81" s="2" t="inlineStr">
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
         <is>
           <t>photo-079</t>
         </is>
       </c>
-      <c r="M81" s="6" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr">
+      <c r="N81" s="6" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0137_1.jpg</t>
         </is>
@@ -11257,8 +11367,9 @@
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="6" t="inlineStr"/>
-      <c r="N82" s="2" t="inlineStr">
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="6" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0138.jpg</t>
         </is>
@@ -11314,13 +11425,14 @@
           <t>Decals</t>
         </is>
       </c>
-      <c r="L83" s="2" t="inlineStr">
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>photo-081</t>
         </is>
       </c>
-      <c r="M83" s="6" t="inlineStr"/>
-      <c r="N83" s="2" t="inlineStr">
+      <c r="N83" s="6" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0138_1.jpg</t>
         </is>
@@ -11372,9 +11484,14 @@
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="6" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr">
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>faces — publishing permission granted 2026-09-16</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="6" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0139.jpg</t>
         </is>
@@ -11428,11 +11545,16 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
+          <t>faces — publishing permission granted 2026-09-16</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
           <t>photo-083</t>
         </is>
       </c>
-      <c r="M85" s="6" t="inlineStr"/>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="N85" s="6" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0139_1.jpg</t>
         </is>
@@ -11485,8 +11607,9 @@
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="6" t="inlineStr"/>
-      <c r="N86" s="2" t="inlineStr">
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="6" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0140.jpg</t>
         </is>
@@ -11538,13 +11661,14 @@
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="inlineStr">
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
         <is>
           <t>photo-085</t>
         </is>
       </c>
-      <c r="M87" s="6" t="inlineStr"/>
-      <c r="N87" s="2" t="inlineStr">
+      <c r="N87" s="6" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0140_1.jpg</t>
         </is>
@@ -11601,8 +11725,9 @@
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="6" t="inlineStr"/>
-      <c r="N88" s="2" t="inlineStr">
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="6" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0141.jpg</t>
         </is>
@@ -11658,13 +11783,14 @@
           <t>Security barriers</t>
         </is>
       </c>
-      <c r="L89" s="2" t="inlineStr">
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
         <is>
           <t>photo-087</t>
         </is>
       </c>
-      <c r="M89" s="6" t="inlineStr"/>
-      <c r="N89" s="2" t="inlineStr">
+      <c r="N89" s="6" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0141_1.jpg</t>
         </is>
@@ -11717,8 +11843,9 @@
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="6" t="inlineStr"/>
-      <c r="N90" s="2" t="inlineStr">
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="6" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0142.jpg</t>
         </is>
@@ -11770,13 +11897,14 @@
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="inlineStr">
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
         <is>
           <t>photo-089</t>
         </is>
       </c>
-      <c r="M91" s="6" t="inlineStr"/>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="N91" s="6" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0142_1.jpg</t>
         </is>
@@ -11829,8 +11957,9 @@
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="6" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr">
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="6" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0143.jpg</t>
         </is>
@@ -11882,13 +12011,14 @@
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="inlineStr">
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
         <is>
           <t>photo-091</t>
         </is>
       </c>
-      <c r="M93" s="6" t="inlineStr"/>
-      <c r="N93" s="2" t="inlineStr">
+      <c r="N93" s="6" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0143_1.jpg</t>
         </is>
@@ -11937,8 +12067,9 @@
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="6" t="inlineStr"/>
-      <c r="N94" s="2" t="inlineStr">
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="6" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0144.jpg</t>
         </is>
@@ -11990,13 +12121,14 @@
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr">
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
         <is>
           <t>photo-093</t>
         </is>
       </c>
-      <c r="M95" s="6" t="inlineStr"/>
-      <c r="N95" s="2" t="inlineStr">
+      <c r="N95" s="6" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0144_1.jpg</t>
         </is>
@@ -12048,9 +12180,14 @@
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="6" t="inlineStr"/>
-      <c r="N96" s="2" t="inlineStr">
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>faces — publishing permission granted 2026-09-16</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="6" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0145.jpg</t>
         </is>
@@ -12104,11 +12241,16 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
+          <t>faces — publishing permission granted 2026-09-16</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
           <t>photo-095</t>
         </is>
       </c>
-      <c r="M97" s="6" t="inlineStr"/>
-      <c r="N97" s="2" t="inlineStr">
+      <c r="N97" s="6" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0145_1.jpg</t>
         </is>
@@ -12161,8 +12303,9 @@
       </c>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="6" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr">
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="6" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0146.jpg</t>
         </is>
@@ -12214,13 +12357,14 @@
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="inlineStr">
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
         <is>
           <t>photo-097</t>
         </is>
       </c>
-      <c r="M99" s="6" t="inlineStr"/>
-      <c r="N99" s="2" t="inlineStr">
+      <c r="N99" s="6" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0146_1.jpg</t>
         </is>
@@ -12273,8 +12417,9 @@
       </c>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="6" t="inlineStr"/>
-      <c r="N100" s="2" t="inlineStr">
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="6" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0147.jpg</t>
         </is>
@@ -12326,13 +12471,14 @@
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="inlineStr">
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
         <is>
           <t>photo-099</t>
         </is>
       </c>
-      <c r="M101" s="6" t="inlineStr"/>
-      <c r="N101" s="2" t="inlineStr">
+      <c r="N101" s="6" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0147_1.jpg</t>
         </is>
@@ -12381,8 +12527,9 @@
       </c>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="6" t="inlineStr"/>
-      <c r="N102" s="2" t="inlineStr">
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="6" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0148.jpg</t>
         </is>
@@ -12431,8 +12578,9 @@
       </c>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr"/>
-      <c r="M103" s="6" t="inlineStr"/>
-      <c r="N103" s="2" t="inlineStr">
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="6" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0149.jpg</t>
         </is>
@@ -12484,13 +12632,14 @@
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="inlineStr">
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr">
         <is>
           <t>photo-102</t>
         </is>
       </c>
-      <c r="M104" s="6" t="inlineStr"/>
-      <c r="N104" s="2" t="inlineStr">
+      <c r="N104" s="6" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0149_1.jpg</t>
         </is>
@@ -12543,8 +12692,9 @@
       </c>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr"/>
-      <c r="M105" s="6" t="inlineStr"/>
-      <c r="N105" s="2" t="inlineStr">
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="6" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0150.jpg</t>
         </is>
@@ -12596,13 +12746,14 @@
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="2" t="inlineStr">
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr">
         <is>
           <t>photo-104</t>
         </is>
       </c>
-      <c r="M106" s="6" t="inlineStr"/>
-      <c r="N106" s="2" t="inlineStr">
+      <c r="N106" s="6" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0150_1.jpg</t>
         </is>
@@ -12655,8 +12806,9 @@
       </c>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr"/>
-      <c r="M107" s="6" t="inlineStr"/>
-      <c r="N107" s="2" t="inlineStr">
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="6" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0151.jpg</t>
         </is>
@@ -12708,13 +12860,14 @@
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="inlineStr">
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr">
         <is>
           <t>photo-106</t>
         </is>
       </c>
-      <c r="M108" s="6" t="inlineStr"/>
-      <c r="N108" s="2" t="inlineStr">
+      <c r="N108" s="6" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0151_1.jpg</t>
         </is>
@@ -12767,8 +12920,9 @@
       </c>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr"/>
-      <c r="M109" s="6" t="inlineStr"/>
-      <c r="N109" s="2" t="inlineStr">
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="6" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0152.jpg</t>
         </is>
@@ -12820,13 +12974,14 @@
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="inlineStr">
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr">
         <is>
           <t>photo-108</t>
         </is>
       </c>
-      <c r="M110" s="6" t="inlineStr"/>
-      <c r="N110" s="2" t="inlineStr">
+      <c r="N110" s="6" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0152_1.jpg</t>
         </is>
@@ -12883,8 +13038,9 @@
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr"/>
-      <c r="M111" s="6" t="inlineStr"/>
-      <c r="N111" s="2" t="inlineStr">
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="6" t="inlineStr"/>
+      <c r="O111" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0153.jpg</t>
         </is>
@@ -12940,13 +13096,14 @@
           <t>Guard tower</t>
         </is>
       </c>
-      <c r="L112" s="2" t="inlineStr">
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr">
         <is>
           <t>photo-110</t>
         </is>
       </c>
-      <c r="M112" s="6" t="inlineStr"/>
-      <c r="N112" s="2" t="inlineStr">
+      <c r="N112" s="6" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0153_1.jpg</t>
         </is>
@@ -13003,8 +13160,9 @@
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr"/>
-      <c r="M113" s="6" t="inlineStr"/>
-      <c r="N113" s="2" t="inlineStr">
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="6" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0154.jpg</t>
         </is>
@@ -13060,13 +13218,14 @@
           <t>Decal</t>
         </is>
       </c>
-      <c r="L114" s="2" t="inlineStr">
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr">
         <is>
           <t>photo-112</t>
         </is>
       </c>
-      <c r="M114" s="6" t="inlineStr"/>
-      <c r="N114" s="2" t="inlineStr">
+      <c r="N114" s="6" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0154_1.jpg</t>
         </is>
@@ -13119,8 +13278,9 @@
       </c>
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr"/>
-      <c r="M115" s="6" t="inlineStr"/>
-      <c r="N115" s="2" t="inlineStr">
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="6" t="inlineStr"/>
+      <c r="O115" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0155.jpg</t>
         </is>
@@ -13172,13 +13332,14 @@
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="inlineStr">
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr">
         <is>
           <t>photo-114</t>
         </is>
       </c>
-      <c r="M116" s="6" t="inlineStr"/>
-      <c r="N116" s="2" t="inlineStr">
+      <c r="N116" s="6" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0155_1.jpg</t>
         </is>
@@ -13231,8 +13392,9 @@
       </c>
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr"/>
-      <c r="M117" s="6" t="inlineStr"/>
-      <c r="N117" s="2" t="inlineStr">
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="6" t="inlineStr"/>
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0156.jpg</t>
         </is>
@@ -13284,13 +13446,14 @@
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="inlineStr">
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr">
         <is>
           <t>photo-116</t>
         </is>
       </c>
-      <c r="M118" s="6" t="inlineStr"/>
-      <c r="N118" s="2" t="inlineStr">
+      <c r="N118" s="6" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0156_1.jpg</t>
         </is>
@@ -13347,8 +13510,9 @@
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr"/>
-      <c r="M119" s="6" t="inlineStr"/>
-      <c r="N119" s="2" t="inlineStr">
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="6" t="inlineStr"/>
+      <c r="O119" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0157.jpg</t>
         </is>
@@ -13404,13 +13568,14 @@
           <t>Security barriers</t>
         </is>
       </c>
-      <c r="L120" s="2" t="inlineStr">
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr">
         <is>
           <t>photo-118</t>
         </is>
       </c>
-      <c r="M120" s="6" t="inlineStr"/>
-      <c r="N120" s="2" t="inlineStr">
+      <c r="N120" s="6" t="inlineStr"/>
+      <c r="O120" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0157_1.jpg</t>
         </is>
@@ -13463,8 +13628,9 @@
       </c>
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr"/>
-      <c r="M121" s="6" t="inlineStr"/>
-      <c r="N121" s="2" t="inlineStr">
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="6" t="inlineStr"/>
+      <c r="O121" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0158.jpg</t>
         </is>
@@ -13516,13 +13682,14 @@
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="2" t="inlineStr">
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr">
         <is>
           <t>photo-120</t>
         </is>
       </c>
-      <c r="M122" s="6" t="inlineStr"/>
-      <c r="N122" s="2" t="inlineStr">
+      <c r="N122" s="6" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0158_1.jpg</t>
         </is>
@@ -13575,8 +13742,9 @@
       </c>
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr"/>
-      <c r="M123" s="6" t="inlineStr"/>
-      <c r="N123" s="2" t="inlineStr">
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="6" t="inlineStr"/>
+      <c r="O123" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0159.jpg</t>
         </is>
@@ -13628,13 +13796,14 @@
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="2" t="inlineStr">
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr">
         <is>
           <t>photo-122</t>
         </is>
       </c>
-      <c r="M124" s="6" t="inlineStr"/>
-      <c r="N124" s="2" t="inlineStr">
+      <c r="N124" s="6" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0159_1.jpg</t>
         </is>
@@ -13687,8 +13856,9 @@
       </c>
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr"/>
-      <c r="M125" s="6" t="inlineStr"/>
-      <c r="N125" s="2" t="inlineStr">
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="6" t="inlineStr"/>
+      <c r="O125" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0160.jpg</t>
         </is>
@@ -13740,13 +13910,14 @@
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="2" t="inlineStr">
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr">
         <is>
           <t>photo-124</t>
         </is>
       </c>
-      <c r="M126" s="6" t="inlineStr"/>
-      <c r="N126" s="2" t="inlineStr">
+      <c r="N126" s="6" t="inlineStr"/>
+      <c r="O126" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0160_1.jpg</t>
         </is>
@@ -13799,8 +13970,9 @@
       </c>
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr"/>
-      <c r="M127" s="6" t="inlineStr"/>
-      <c r="N127" s="2" t="inlineStr">
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="6" t="inlineStr"/>
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0161.jpg</t>
         </is>
@@ -13852,13 +14024,14 @@
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="2" t="inlineStr">
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr">
         <is>
           <t>photo-126</t>
         </is>
       </c>
-      <c r="M128" s="6" t="inlineStr"/>
-      <c r="N128" s="2" t="inlineStr">
+      <c r="N128" s="6" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0161_1.jpg</t>
         </is>
@@ -13907,8 +14080,9 @@
       </c>
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr"/>
-      <c r="M129" s="6" t="inlineStr"/>
-      <c r="N129" s="2" t="inlineStr">
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="6" t="inlineStr"/>
+      <c r="O129" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0162.jpg</t>
         </is>
@@ -13960,13 +14134,14 @@
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr"/>
-      <c r="L130" s="2" t="inlineStr">
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr">
         <is>
           <t>photo-128</t>
         </is>
       </c>
-      <c r="M130" s="6" t="inlineStr"/>
-      <c r="N130" s="2" t="inlineStr">
+      <c r="N130" s="6" t="inlineStr"/>
+      <c r="O130" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0162_1.jpg</t>
         </is>
@@ -14015,8 +14190,9 @@
       </c>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr"/>
-      <c r="M131" s="6" t="inlineStr"/>
-      <c r="N131" s="2" t="inlineStr">
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="6" t="inlineStr"/>
+      <c r="O131" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0163.jpg</t>
         </is>
@@ -14068,13 +14244,14 @@
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="2" t="inlineStr">
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr">
         <is>
           <t>photo-130</t>
         </is>
       </c>
-      <c r="M132" s="6" t="inlineStr"/>
-      <c r="N132" s="2" t="inlineStr">
+      <c r="N132" s="6" t="inlineStr"/>
+      <c r="O132" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0163_1.jpg</t>
         </is>
@@ -14127,8 +14304,9 @@
       </c>
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr"/>
-      <c r="M133" s="6" t="inlineStr"/>
-      <c r="N133" s="2" t="inlineStr">
+      <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="6" t="inlineStr"/>
+      <c r="O133" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0164.jpg</t>
         </is>
@@ -14180,13 +14358,14 @@
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="2" t="inlineStr">
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr">
         <is>
           <t>photo-132</t>
         </is>
       </c>
-      <c r="M134" s="6" t="inlineStr"/>
-      <c r="N134" s="2" t="inlineStr">
+      <c r="N134" s="6" t="inlineStr"/>
+      <c r="O134" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0164_1.jpg</t>
         </is>
@@ -14239,8 +14418,9 @@
       </c>
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr"/>
-      <c r="M135" s="6" t="inlineStr"/>
-      <c r="N135" s="2" t="inlineStr">
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="6" t="inlineStr"/>
+      <c r="O135" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0165.jpg</t>
         </is>
@@ -14292,13 +14472,14 @@
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr"/>
-      <c r="L136" s="2" t="inlineStr">
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr">
         <is>
           <t>photo-134</t>
         </is>
       </c>
-      <c r="M136" s="6" t="inlineStr"/>
-      <c r="N136" s="2" t="inlineStr">
+      <c r="N136" s="6" t="inlineStr"/>
+      <c r="O136" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0165_1.jpg</t>
         </is>
@@ -14347,8 +14528,9 @@
       </c>
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr"/>
-      <c r="M137" s="6" t="inlineStr"/>
-      <c r="N137" s="2" t="inlineStr">
+      <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="6" t="inlineStr"/>
+      <c r="O137" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0166.jpg</t>
         </is>
@@ -14400,13 +14582,14 @@
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr"/>
-      <c r="L138" s="2" t="inlineStr">
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr">
         <is>
           <t>photo-136</t>
         </is>
       </c>
-      <c r="M138" s="6" t="inlineStr"/>
-      <c r="N138" s="2" t="inlineStr">
+      <c r="N138" s="6" t="inlineStr"/>
+      <c r="O138" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0166_1.jpg</t>
         </is>
@@ -14459,8 +14642,9 @@
       </c>
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr"/>
-      <c r="M139" s="6" t="inlineStr"/>
-      <c r="N139" s="2" t="inlineStr">
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="6" t="inlineStr"/>
+      <c r="O139" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0167.jpg</t>
         </is>
@@ -14512,13 +14696,14 @@
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr"/>
-      <c r="L140" s="2" t="inlineStr">
+      <c r="L140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr">
         <is>
           <t>photo-138</t>
         </is>
       </c>
-      <c r="M140" s="6" t="inlineStr"/>
-      <c r="N140" s="2" t="inlineStr">
+      <c r="N140" s="6" t="inlineStr"/>
+      <c r="O140" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0167_1.jpg</t>
         </is>
@@ -14575,8 +14760,9 @@
         </is>
       </c>
       <c r="L141" s="2" t="inlineStr"/>
-      <c r="M141" s="6" t="inlineStr"/>
-      <c r="N141" s="2" t="inlineStr">
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="6" t="inlineStr"/>
+      <c r="O141" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0168.jpg</t>
         </is>
@@ -14632,13 +14818,14 @@
           <t>Police emblems on barriers</t>
         </is>
       </c>
-      <c r="L142" s="2" t="inlineStr">
+      <c r="L142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr">
         <is>
           <t>photo-140</t>
         </is>
       </c>
-      <c r="M142" s="6" t="inlineStr"/>
-      <c r="N142" s="2" t="inlineStr">
+      <c r="N142" s="6" t="inlineStr"/>
+      <c r="O142" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0168_1.jpg</t>
         </is>
@@ -14687,8 +14874,9 @@
       </c>
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr"/>
-      <c r="M143" s="6" t="inlineStr"/>
-      <c r="N143" s="2" t="inlineStr">
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="6" t="inlineStr"/>
+      <c r="O143" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0169.jpg</t>
         </is>
@@ -14740,13 +14928,14 @@
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr"/>
-      <c r="L144" s="2" t="inlineStr">
+      <c r="L144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="inlineStr">
         <is>
           <t>photo-142</t>
         </is>
       </c>
-      <c r="M144" s="6" t="inlineStr"/>
-      <c r="N144" s="2" t="inlineStr">
+      <c r="N144" s="6" t="inlineStr"/>
+      <c r="O144" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0169_1.jpg</t>
         </is>
@@ -14799,8 +14988,9 @@
       </c>
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr"/>
-      <c r="M145" s="6" t="inlineStr"/>
-      <c r="N145" s="2" t="inlineStr">
+      <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="6" t="inlineStr"/>
+      <c r="O145" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0170.jpg</t>
         </is>
@@ -14852,13 +15042,14 @@
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
-      <c r="L146" s="2" t="inlineStr">
+      <c r="L146" s="2" t="inlineStr"/>
+      <c r="M146" s="2" t="inlineStr">
         <is>
           <t>photo-144</t>
         </is>
       </c>
-      <c r="M146" s="6" t="inlineStr"/>
-      <c r="N146" s="2" t="inlineStr">
+      <c r="N146" s="6" t="inlineStr"/>
+      <c r="O146" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0170_1.jpg</t>
         </is>
@@ -14911,8 +15102,9 @@
       </c>
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr"/>
-      <c r="M147" s="6" t="inlineStr"/>
-      <c r="N147" s="2" t="inlineStr">
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="6" t="inlineStr"/>
+      <c r="O147" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0171.jpg</t>
         </is>
@@ -14964,13 +15156,14 @@
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr"/>
-      <c r="L148" s="2" t="inlineStr">
+      <c r="L148" s="2" t="inlineStr"/>
+      <c r="M148" s="2" t="inlineStr">
         <is>
           <t>photo-146</t>
         </is>
       </c>
-      <c r="M148" s="6" t="inlineStr"/>
-      <c r="N148" s="2" t="inlineStr">
+      <c r="N148" s="6" t="inlineStr"/>
+      <c r="O148" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0171_1.jpg</t>
         </is>
@@ -15023,8 +15216,9 @@
       </c>
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr"/>
-      <c r="M149" s="6" t="inlineStr"/>
-      <c r="N149" s="2" t="inlineStr">
+      <c r="M149" s="2" t="inlineStr"/>
+      <c r="N149" s="6" t="inlineStr"/>
+      <c r="O149" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0172.jpg</t>
         </is>
@@ -15076,13 +15270,14 @@
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
-      <c r="L150" s="2" t="inlineStr">
+      <c r="L150" s="2" t="inlineStr"/>
+      <c r="M150" s="2" t="inlineStr">
         <is>
           <t>photo-148</t>
         </is>
       </c>
-      <c r="M150" s="6" t="inlineStr"/>
-      <c r="N150" s="2" t="inlineStr">
+      <c r="N150" s="6" t="inlineStr"/>
+      <c r="O150" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0172_1.jpg</t>
         </is>
@@ -15135,8 +15330,9 @@
       </c>
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr"/>
-      <c r="M151" s="6" t="inlineStr"/>
-      <c r="N151" s="2" t="inlineStr">
+      <c r="M151" s="2" t="inlineStr"/>
+      <c r="N151" s="6" t="inlineStr"/>
+      <c r="O151" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0173.jpg</t>
         </is>
@@ -15188,13 +15384,14 @@
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
-      <c r="L152" s="2" t="inlineStr">
+      <c r="L152" s="2" t="inlineStr"/>
+      <c r="M152" s="2" t="inlineStr">
         <is>
           <t>photo-150</t>
         </is>
       </c>
-      <c r="M152" s="6" t="inlineStr"/>
-      <c r="N152" s="2" t="inlineStr">
+      <c r="N152" s="6" t="inlineStr"/>
+      <c r="O152" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0173_1.jpg</t>
         </is>
@@ -15243,8 +15440,9 @@
       </c>
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr"/>
-      <c r="M153" s="6" t="inlineStr"/>
-      <c r="N153" s="2" t="inlineStr">
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="6" t="inlineStr"/>
+      <c r="O153" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0174.jpg</t>
         </is>
@@ -15296,13 +15494,14 @@
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
-      <c r="L154" s="2" t="inlineStr">
+      <c r="L154" s="2" t="inlineStr"/>
+      <c r="M154" s="2" t="inlineStr">
         <is>
           <t>photo-152</t>
         </is>
       </c>
-      <c r="M154" s="6" t="inlineStr"/>
-      <c r="N154" s="2" t="inlineStr">
+      <c r="N154" s="6" t="inlineStr"/>
+      <c r="O154" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0174_1.jpg</t>
         </is>
@@ -15359,8 +15558,9 @@
         </is>
       </c>
       <c r="L155" s="2" t="inlineStr"/>
-      <c r="M155" s="6" t="inlineStr"/>
-      <c r="N155" s="2" t="inlineStr">
+      <c r="M155" s="2" t="inlineStr"/>
+      <c r="N155" s="6" t="inlineStr"/>
+      <c r="O155" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0175.jpg</t>
         </is>
@@ -15416,13 +15616,14 @@
           <t>Printed stamp: Ahmed A.B 20 February 2024 3:10 pm</t>
         </is>
       </c>
-      <c r="L156" s="2" t="inlineStr">
+      <c r="L156" s="2" t="inlineStr"/>
+      <c r="M156" s="2" t="inlineStr">
         <is>
           <t>photo-154</t>
         </is>
       </c>
-      <c r="M156" s="6" t="inlineStr"/>
-      <c r="N156" s="2" t="inlineStr">
+      <c r="N156" s="6" t="inlineStr"/>
+      <c r="O156" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0175_1.jpg</t>
         </is>
@@ -15479,8 +15680,9 @@
         </is>
       </c>
       <c r="L157" s="2" t="inlineStr"/>
-      <c r="M157" s="6" t="inlineStr"/>
-      <c r="N157" s="2" t="inlineStr">
+      <c r="M157" s="2" t="inlineStr"/>
+      <c r="N157" s="6" t="inlineStr"/>
+      <c r="O157" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0176.jpg</t>
         </is>
@@ -15536,13 +15738,14 @@
           <t>Printed date stamp</t>
         </is>
       </c>
-      <c r="L158" s="2" t="inlineStr">
+      <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr">
         <is>
           <t>photo-156</t>
         </is>
       </c>
-      <c r="M158" s="6" t="inlineStr"/>
-      <c r="N158" s="2" t="inlineStr">
+      <c r="N158" s="6" t="inlineStr"/>
+      <c r="O158" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0176_1.jpg</t>
         </is>
@@ -15599,8 +15802,9 @@
         </is>
       </c>
       <c r="L159" s="2" t="inlineStr"/>
-      <c r="M159" s="6" t="inlineStr"/>
-      <c r="N159" s="2" t="inlineStr">
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="6" t="inlineStr"/>
+      <c r="O159" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0177.jpg</t>
         </is>
@@ -15656,13 +15860,14 @@
           <t>Printed date stamp</t>
         </is>
       </c>
-      <c r="L160" s="2" t="inlineStr">
+      <c r="L160" s="2" t="inlineStr"/>
+      <c r="M160" s="2" t="inlineStr">
         <is>
           <t>photo-158</t>
         </is>
       </c>
-      <c r="M160" s="6" t="inlineStr"/>
-      <c r="N160" s="2" t="inlineStr">
+      <c r="N160" s="6" t="inlineStr"/>
+      <c r="O160" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0177_1.jpg</t>
         </is>
@@ -15715,8 +15920,9 @@
       </c>
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr"/>
-      <c r="M161" s="6" t="inlineStr"/>
-      <c r="N161" s="2" t="inlineStr">
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="6" t="inlineStr"/>
+      <c r="O161" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0178.jpg</t>
         </is>
@@ -15768,13 +15974,14 @@
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="2" t="inlineStr">
+      <c r="L162" s="2" t="inlineStr"/>
+      <c r="M162" s="2" t="inlineStr">
         <is>
           <t>photo-160</t>
         </is>
       </c>
-      <c r="M162" s="6" t="inlineStr"/>
-      <c r="N162" s="2" t="inlineStr">
+      <c r="N162" s="6" t="inlineStr"/>
+      <c r="O162" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0178_1.jpg</t>
         </is>
@@ -15830,9 +16037,14 @@
           <t>Third-party photographer watermark</t>
         </is>
       </c>
-      <c r="L163" s="2" t="inlineStr"/>
-      <c r="M163" s="6" t="inlineStr"/>
-      <c r="N163" s="2" t="inlineStr">
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>photographer's mark — company work with publishing rights; the mark is cropped out (2026-09-16)</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="6" t="inlineStr"/>
+      <c r="O163" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0179.jpg</t>
         </is>
@@ -15890,11 +16102,16 @@
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
+          <t>photographer's mark — company work with publishing rights; the mark is cropped out (2026-09-16)</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
           <t>photo-162</t>
         </is>
       </c>
-      <c r="M164" s="6" t="inlineStr"/>
-      <c r="N164" s="2" t="inlineStr">
+      <c r="N164" s="6" t="inlineStr"/>
+      <c r="O164" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0179_1.jpg</t>
         </is>
@@ -15947,8 +16164,9 @@
       </c>
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr"/>
-      <c r="M165" s="6" t="inlineStr"/>
-      <c r="N165" s="2" t="inlineStr">
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="6" t="inlineStr"/>
+      <c r="O165" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0180.jpg</t>
         </is>
@@ -16004,9 +16222,14 @@
           <t>Third-party photographer watermark</t>
         </is>
       </c>
-      <c r="L166" s="2" t="inlineStr"/>
-      <c r="M166" s="6" t="inlineStr"/>
-      <c r="N166" s="2" t="inlineStr">
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>photographer's mark — company work with publishing rights, but it cannot be cropped cleanly (2026-09-16)</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="6" t="inlineStr"/>
+      <c r="O166" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0181.jpg</t>
         </is>
@@ -16064,11 +16287,16 @@
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
+          <t>photographer's mark — company work with publishing rights, but it cannot be cropped cleanly (2026-09-16)</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
           <t>photo-165</t>
         </is>
       </c>
-      <c r="M167" s="6" t="inlineStr"/>
-      <c r="N167" s="2" t="inlineStr">
+      <c r="N167" s="6" t="inlineStr"/>
+      <c r="O167" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0181_1.jpg</t>
         </is>
@@ -16121,8 +16349,9 @@
       </c>
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr"/>
-      <c r="M168" s="6" t="inlineStr"/>
-      <c r="N168" s="2" t="inlineStr">
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="6" t="inlineStr"/>
+      <c r="O168" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0182.jpg</t>
         </is>
@@ -16175,8 +16404,9 @@
       </c>
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr"/>
-      <c r="M169" s="6" t="inlineStr"/>
-      <c r="N169" s="2" t="inlineStr">
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="6" t="inlineStr"/>
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0183.jpg</t>
         </is>
@@ -16225,8 +16455,9 @@
       </c>
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr"/>
-      <c r="M170" s="6" t="inlineStr"/>
-      <c r="N170" s="2" t="inlineStr">
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="6" t="inlineStr"/>
+      <c r="O170" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0184.jpg</t>
         </is>
@@ -16279,8 +16510,9 @@
       </c>
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr"/>
-      <c r="M171" s="6" t="inlineStr"/>
-      <c r="N171" s="2" t="inlineStr">
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="6" t="inlineStr"/>
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0185.jpg</t>
         </is>
@@ -16333,8 +16565,9 @@
       </c>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr"/>
-      <c r="M172" s="6" t="inlineStr"/>
-      <c r="N172" s="2" t="inlineStr">
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="6" t="inlineStr"/>
+      <c r="O172" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0186.jpg</t>
         </is>
@@ -16387,8 +16620,9 @@
       </c>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr"/>
-      <c r="M173" s="6" t="inlineStr"/>
-      <c r="N173" s="2" t="inlineStr">
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="6" t="inlineStr"/>
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0187.jpg</t>
         </is>
@@ -16441,8 +16675,9 @@
       </c>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr"/>
-      <c r="M174" s="6" t="inlineStr"/>
-      <c r="N174" s="2" t="inlineStr">
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="6" t="inlineStr"/>
+      <c r="O174" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0188.jpg</t>
         </is>
@@ -16495,8 +16730,9 @@
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr"/>
-      <c r="M175" s="6" t="inlineStr"/>
-      <c r="N175" s="2" t="inlineStr">
+      <c r="M175" s="2" t="inlineStr"/>
+      <c r="N175" s="6" t="inlineStr"/>
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0189.jpg</t>
         </is>
@@ -16549,8 +16785,9 @@
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr"/>
-      <c r="M176" s="6" t="inlineStr"/>
-      <c r="N176" s="2" t="inlineStr">
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="6" t="inlineStr"/>
+      <c r="O176" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0191.jpg</t>
         </is>
@@ -16603,8 +16840,9 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr"/>
-      <c r="M177" s="6" t="inlineStr"/>
-      <c r="N177" s="2" t="inlineStr">
+      <c r="M177" s="2" t="inlineStr"/>
+      <c r="N177" s="6" t="inlineStr"/>
+      <c r="O177" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0192.jpg</t>
         </is>
@@ -16657,8 +16895,9 @@
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr"/>
-      <c r="M178" s="6" t="inlineStr"/>
-      <c r="N178" s="2" t="inlineStr">
+      <c r="M178" s="2" t="inlineStr"/>
+      <c r="N178" s="6" t="inlineStr"/>
+      <c r="O178" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0193.jpg</t>
         </is>
@@ -16711,8 +16950,9 @@
       </c>
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr"/>
-      <c r="M179" s="6" t="inlineStr"/>
-      <c r="N179" s="2" t="inlineStr">
+      <c r="M179" s="2" t="inlineStr"/>
+      <c r="N179" s="6" t="inlineStr"/>
+      <c r="O179" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0194.jpg</t>
         </is>
@@ -16765,8 +17005,9 @@
       </c>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr"/>
-      <c r="M180" s="6" t="inlineStr"/>
-      <c r="N180" s="2" t="inlineStr">
+      <c r="M180" s="2" t="inlineStr"/>
+      <c r="N180" s="6" t="inlineStr"/>
+      <c r="O180" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0195.jpg</t>
         </is>
@@ -16815,8 +17056,9 @@
       </c>
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr"/>
-      <c r="M181" s="6" t="inlineStr"/>
-      <c r="N181" s="2" t="inlineStr">
+      <c r="M181" s="2" t="inlineStr"/>
+      <c r="N181" s="6" t="inlineStr"/>
+      <c r="O181" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0196.jpg</t>
         </is>
@@ -16869,8 +17111,9 @@
       </c>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr"/>
-      <c r="M182" s="6" t="inlineStr"/>
-      <c r="N182" s="2" t="inlineStr">
+      <c r="M182" s="2" t="inlineStr"/>
+      <c r="N182" s="6" t="inlineStr"/>
+      <c r="O182" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0197.jpg</t>
         </is>
@@ -16919,8 +17162,9 @@
       </c>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
-      <c r="M183" s="6" t="inlineStr"/>
-      <c r="N183" s="2" t="inlineStr">
+      <c r="M183" s="2" t="inlineStr"/>
+      <c r="N183" s="6" t="inlineStr"/>
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0198.jpg</t>
         </is>
@@ -16973,8 +17217,9 @@
       </c>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr"/>
-      <c r="M184" s="6" t="inlineStr"/>
-      <c r="N184" s="2" t="inlineStr">
+      <c r="M184" s="2" t="inlineStr"/>
+      <c r="N184" s="6" t="inlineStr"/>
+      <c r="O184" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0199.jpg</t>
         </is>
@@ -17027,8 +17272,9 @@
       </c>
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr"/>
-      <c r="M185" s="6" t="inlineStr"/>
-      <c r="N185" s="2" t="inlineStr">
+      <c r="M185" s="2" t="inlineStr"/>
+      <c r="N185" s="6" t="inlineStr"/>
+      <c r="O185" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0200.jpg</t>
         </is>
@@ -17081,8 +17327,9 @@
       </c>
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr"/>
-      <c r="M186" s="6" t="inlineStr"/>
-      <c r="N186" s="2" t="inlineStr">
+      <c r="M186" s="2" t="inlineStr"/>
+      <c r="N186" s="6" t="inlineStr"/>
+      <c r="O186" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0201.jpg</t>
         </is>
@@ -17135,8 +17382,9 @@
       </c>
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr"/>
-      <c r="M187" s="6" t="inlineStr"/>
-      <c r="N187" s="2" t="inlineStr">
+      <c r="M187" s="2" t="inlineStr"/>
+      <c r="N187" s="6" t="inlineStr"/>
+      <c r="O187" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0202.jpg</t>
         </is>
@@ -17189,8 +17437,9 @@
       </c>
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr"/>
-      <c r="M188" s="6" t="inlineStr"/>
-      <c r="N188" s="2" t="inlineStr">
+      <c r="M188" s="2" t="inlineStr"/>
+      <c r="N188" s="6" t="inlineStr"/>
+      <c r="O188" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0203.jpg</t>
         </is>
@@ -17243,8 +17492,9 @@
       </c>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
-      <c r="M189" s="6" t="inlineStr"/>
-      <c r="N189" s="2" t="inlineStr">
+      <c r="M189" s="2" t="inlineStr"/>
+      <c r="N189" s="6" t="inlineStr"/>
+      <c r="O189" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0204.jpg</t>
         </is>
@@ -17297,8 +17547,9 @@
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
-      <c r="M190" s="6" t="inlineStr"/>
-      <c r="N190" s="2" t="inlineStr">
+      <c r="M190" s="2" t="inlineStr"/>
+      <c r="N190" s="6" t="inlineStr"/>
+      <c r="O190" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0205.jpg</t>
         </is>
@@ -17351,8 +17602,9 @@
       </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
-      <c r="M191" s="6" t="inlineStr"/>
-      <c r="N191" s="2" t="inlineStr">
+      <c r="M191" s="2" t="inlineStr"/>
+      <c r="N191" s="6" t="inlineStr"/>
+      <c r="O191" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0206.jpg</t>
         </is>
@@ -17405,8 +17657,9 @@
       </c>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
-      <c r="M192" s="6" t="inlineStr"/>
-      <c r="N192" s="2" t="inlineStr">
+      <c r="M192" s="2" t="inlineStr"/>
+      <c r="N192" s="6" t="inlineStr"/>
+      <c r="O192" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0207.jpg</t>
         </is>
@@ -17455,8 +17708,9 @@
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
-      <c r="M193" s="6" t="inlineStr"/>
-      <c r="N193" s="2" t="inlineStr">
+      <c r="M193" s="2" t="inlineStr"/>
+      <c r="N193" s="6" t="inlineStr"/>
+      <c r="O193" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0210.jpg</t>
         </is>
@@ -17508,13 +17762,14 @@
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
-      <c r="L194" s="2" t="inlineStr">
+      <c r="L194" s="2" t="inlineStr"/>
+      <c r="M194" s="2" t="inlineStr">
         <is>
           <t>photo-192</t>
         </is>
       </c>
-      <c r="M194" s="6" t="inlineStr"/>
-      <c r="N194" s="2" t="inlineStr">
+      <c r="N194" s="6" t="inlineStr"/>
+      <c r="O194" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0210_1.jpg</t>
         </is>
@@ -17567,8 +17822,9 @@
       </c>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
-      <c r="M195" s="6" t="inlineStr"/>
-      <c r="N195" s="2" t="inlineStr">
+      <c r="M195" s="2" t="inlineStr"/>
+      <c r="N195" s="6" t="inlineStr"/>
+      <c r="O195" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0211.jpg</t>
         </is>
@@ -17620,13 +17876,14 @@
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr"/>
-      <c r="L196" s="2" t="inlineStr">
+      <c r="L196" s="2" t="inlineStr"/>
+      <c r="M196" s="2" t="inlineStr">
         <is>
           <t>photo-194</t>
         </is>
       </c>
-      <c r="M196" s="6" t="inlineStr"/>
-      <c r="N196" s="2" t="inlineStr">
+      <c r="N196" s="6" t="inlineStr"/>
+      <c r="O196" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0211_1.jpg</t>
         </is>
@@ -17675,8 +17932,9 @@
       </c>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr"/>
-      <c r="M197" s="6" t="inlineStr"/>
-      <c r="N197" s="2" t="inlineStr">
+      <c r="M197" s="2" t="inlineStr"/>
+      <c r="N197" s="6" t="inlineStr"/>
+      <c r="O197" s="2" t="inlineStr">
         <is>
           <t>IMG-20260913-WA0213.jpg</t>
         </is>
@@ -17725,8 +17983,9 @@
       </c>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr"/>
-      <c r="M198" s="6" t="inlineStr"/>
-      <c r="N198" s="2" t="inlineStr">
+      <c r="M198" s="2" t="inlineStr"/>
+      <c r="N198" s="6" t="inlineStr"/>
+      <c r="O198" s="2" t="inlineStr">
         <is>
           <t>VID-20260913-WA0208.mp4</t>
         </is>
@@ -17779,8 +18038,9 @@
       </c>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
-      <c r="M199" s="6" t="inlineStr"/>
-      <c r="N199" s="2" t="inlineStr">
+      <c r="M199" s="2" t="inlineStr"/>
+      <c r="N199" s="6" t="inlineStr"/>
+      <c r="O199" s="2" t="inlineStr">
         <is>
           <t>VID-20260913-WA0209.mp4</t>
         </is>
@@ -17829,8 +18089,9 @@
       </c>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr"/>
-      <c r="M200" s="6" t="inlineStr"/>
-      <c r="N200" s="2" t="inlineStr">
+      <c r="M200" s="2" t="inlineStr"/>
+      <c r="N200" s="6" t="inlineStr"/>
+      <c r="O200" s="2" t="inlineStr">
         <is>
           <t>VID-20260913-WA0212.mp4</t>
         </is>
@@ -17883,8 +18144,9 @@
       </c>
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr"/>
-      <c r="M201" s="6" t="inlineStr"/>
-      <c r="N201" s="2" t="inlineStr">
+      <c r="M201" s="2" t="inlineStr"/>
+      <c r="N201" s="6" t="inlineStr"/>
+      <c r="O201" s="2" t="inlineStr">
         <is>
           <t>VID-20260913-WA0214.mp4</t>
         </is>
@@ -17936,13 +18198,14 @@
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr"/>
-      <c r="L202" s="2" t="inlineStr">
+      <c r="L202" s="2" t="inlineStr"/>
+      <c r="M202" s="2" t="inlineStr">
         <is>
           <t>video-004</t>
         </is>
       </c>
-      <c r="M202" s="6" t="inlineStr"/>
-      <c r="N202" s="2" t="inlineStr">
+      <c r="N202" s="6" t="inlineStr"/>
+      <c r="O202" s="2" t="inlineStr">
         <is>
           <t>VID-20260913-WA0214_1.mp4</t>
         </is>
@@ -17995,8 +18258,9 @@
       </c>
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr"/>
-      <c r="M203" s="6" t="inlineStr"/>
-      <c r="N203" s="2" t="inlineStr">
+      <c r="M203" s="2" t="inlineStr"/>
+      <c r="N203" s="6" t="inlineStr"/>
+      <c r="O203" s="2" t="inlineStr">
         <is>
           <t>VID-20260913-WA0215.mp4</t>
         </is>
@@ -18049,8 +18313,9 @@
       </c>
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr"/>
-      <c r="M204" s="6" t="inlineStr"/>
-      <c r="N204" s="2" t="inlineStr">
+      <c r="M204" s="2" t="inlineStr"/>
+      <c r="N204" s="6" t="inlineStr"/>
+      <c r="O204" s="2" t="inlineStr">
         <is>
           <t>VID-20260913-WA0216.mp4</t>
         </is>
@@ -18103,8 +18368,9 @@
       </c>
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr"/>
-      <c r="M205" s="6" t="inlineStr"/>
-      <c r="N205" s="2" t="inlineStr">
+      <c r="M205" s="2" t="inlineStr"/>
+      <c r="N205" s="6" t="inlineStr"/>
+      <c r="O205" s="2" t="inlineStr">
         <is>
           <t>VID-20260913-WA0232.mp4</t>
         </is>
@@ -18153,8 +18419,9 @@
       </c>
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr"/>
-      <c r="M206" s="6" t="inlineStr"/>
-      <c r="N206" s="2" t="inlineStr">
+      <c r="M206" s="2" t="inlineStr"/>
+      <c r="N206" s="6" t="inlineStr"/>
+      <c r="O206" s="2" t="inlineStr">
         <is>
           <t>VID-20260913-WA0233.mp4</t>
         </is>
@@ -18207,8 +18474,9 @@
       </c>
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr"/>
-      <c r="M207" s="6" t="inlineStr"/>
-      <c r="N207" s="2" t="inlineStr">
+      <c r="M207" s="2" t="inlineStr"/>
+      <c r="N207" s="6" t="inlineStr"/>
+      <c r="O207" s="2" t="inlineStr">
         <is>
           <t>VID-20260913-WA0234.mp4</t>
         </is>
@@ -18257,8 +18525,9 @@
       </c>
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="2" t="inlineStr"/>
-      <c r="M208" s="6" t="inlineStr"/>
-      <c r="N208" s="2" t="inlineStr">
+      <c r="M208" s="2" t="inlineStr"/>
+      <c r="N208" s="6" t="inlineStr"/>
+      <c r="O208" s="2" t="inlineStr">
         <is>
           <t>VID-20260913-WA0235.mp4</t>
         </is>
@@ -18307,8 +18576,9 @@
       </c>
       <c r="K209" s="2" t="inlineStr"/>
       <c r="L209" s="2" t="inlineStr"/>
-      <c r="M209" s="6" t="inlineStr"/>
-      <c r="N209" s="2" t="inlineStr">
+      <c r="M209" s="2" t="inlineStr"/>
+      <c r="N209" s="6" t="inlineStr"/>
+      <c r="O209" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0000.mp4</t>
         </is>
@@ -18357,8 +18627,9 @@
       </c>
       <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="2" t="inlineStr"/>
-      <c r="M210" s="6" t="inlineStr"/>
-      <c r="N210" s="2" t="inlineStr">
+      <c r="M210" s="2" t="inlineStr"/>
+      <c r="N210" s="6" t="inlineStr"/>
+      <c r="O210" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0004.mp4</t>
         </is>
@@ -18410,13 +18681,14 @@
         </is>
       </c>
       <c r="K211" s="2" t="inlineStr"/>
-      <c r="L211" s="2" t="inlineStr">
+      <c r="L211" s="2" t="inlineStr"/>
+      <c r="M211" s="2" t="inlineStr">
         <is>
           <t>video-003</t>
         </is>
       </c>
-      <c r="M211" s="6" t="inlineStr"/>
-      <c r="N211" s="2" t="inlineStr">
+      <c r="N211" s="6" t="inlineStr"/>
+      <c r="O211" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0005.mp4</t>
         </is>
@@ -18465,8 +18737,9 @@
       </c>
       <c r="K212" s="2" t="inlineStr"/>
       <c r="L212" s="2" t="inlineStr"/>
-      <c r="M212" s="6" t="inlineStr"/>
-      <c r="N212" s="2" t="inlineStr">
+      <c r="M212" s="2" t="inlineStr"/>
+      <c r="N212" s="6" t="inlineStr"/>
+      <c r="O212" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0006.mp4</t>
         </is>
@@ -18522,9 +18795,14 @@
           <t>Third-party logo "SG … Group" on the vest</t>
         </is>
       </c>
-      <c r="L213" s="2" t="inlineStr"/>
-      <c r="M213" s="6" t="inlineStr"/>
-      <c r="N213" s="2" t="inlineStr">
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>third-party "SG" logo — partner contractor, cleared to publish 2026-09-16</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="inlineStr"/>
+      <c r="N213" s="6" t="inlineStr"/>
+      <c r="O213" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0007.mp4</t>
         </is>
@@ -18577,8 +18855,9 @@
       </c>
       <c r="K214" s="2" t="inlineStr"/>
       <c r="L214" s="2" t="inlineStr"/>
-      <c r="M214" s="6" t="inlineStr"/>
-      <c r="N214" s="2" t="inlineStr">
+      <c r="M214" s="2" t="inlineStr"/>
+      <c r="N214" s="6" t="inlineStr"/>
+      <c r="O214" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0008.mp4</t>
         </is>
@@ -18627,8 +18906,9 @@
       </c>
       <c r="K215" s="2" t="inlineStr"/>
       <c r="L215" s="2" t="inlineStr"/>
-      <c r="M215" s="6" t="inlineStr"/>
-      <c r="N215" s="2" t="inlineStr">
+      <c r="M215" s="2" t="inlineStr"/>
+      <c r="N215" s="6" t="inlineStr"/>
+      <c r="O215" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0020.mp4</t>
         </is>
@@ -18677,8 +18957,9 @@
       </c>
       <c r="K216" s="2" t="inlineStr"/>
       <c r="L216" s="2" t="inlineStr"/>
-      <c r="M216" s="6" t="inlineStr"/>
-      <c r="N216" s="2" t="inlineStr">
+      <c r="M216" s="2" t="inlineStr"/>
+      <c r="N216" s="6" t="inlineStr"/>
+      <c r="O216" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0021.mp4</t>
         </is>
@@ -18727,8 +19008,9 @@
       </c>
       <c r="K217" s="2" t="inlineStr"/>
       <c r="L217" s="2" t="inlineStr"/>
-      <c r="M217" s="6" t="inlineStr"/>
-      <c r="N217" s="2" t="inlineStr">
+      <c r="M217" s="2" t="inlineStr"/>
+      <c r="N217" s="6" t="inlineStr"/>
+      <c r="O217" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0022.mp4</t>
         </is>
@@ -18781,8 +19063,9 @@
       </c>
       <c r="K218" s="2" t="inlineStr"/>
       <c r="L218" s="2" t="inlineStr"/>
-      <c r="M218" s="6" t="inlineStr"/>
-      <c r="N218" s="2" t="inlineStr">
+      <c r="M218" s="2" t="inlineStr"/>
+      <c r="N218" s="6" t="inlineStr"/>
+      <c r="O218" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0024.mp4</t>
         </is>
@@ -18831,8 +19114,9 @@
       </c>
       <c r="K219" s="2" t="inlineStr"/>
       <c r="L219" s="2" t="inlineStr"/>
-      <c r="M219" s="6" t="inlineStr"/>
-      <c r="N219" s="2" t="inlineStr">
+      <c r="M219" s="2" t="inlineStr"/>
+      <c r="N219" s="6" t="inlineStr"/>
+      <c r="O219" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0025.mp4</t>
         </is>
@@ -18885,8 +19169,9 @@
       </c>
       <c r="K220" s="2" t="inlineStr"/>
       <c r="L220" s="2" t="inlineStr"/>
-      <c r="M220" s="6" t="inlineStr"/>
-      <c r="N220" s="2" t="inlineStr">
+      <c r="M220" s="2" t="inlineStr"/>
+      <c r="N220" s="6" t="inlineStr"/>
+      <c r="O220" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0026.mp4</t>
         </is>
@@ -18939,8 +19224,9 @@
       </c>
       <c r="K221" s="2" t="inlineStr"/>
       <c r="L221" s="2" t="inlineStr"/>
-      <c r="M221" s="6" t="inlineStr"/>
-      <c r="N221" s="2" t="inlineStr">
+      <c r="M221" s="2" t="inlineStr"/>
+      <c r="N221" s="6" t="inlineStr"/>
+      <c r="O221" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0027.mp4</t>
         </is>
@@ -18993,8 +19279,9 @@
       </c>
       <c r="K222" s="2" t="inlineStr"/>
       <c r="L222" s="2" t="inlineStr"/>
-      <c r="M222" s="6" t="inlineStr"/>
-      <c r="N222" s="2" t="inlineStr">
+      <c r="M222" s="2" t="inlineStr"/>
+      <c r="N222" s="6" t="inlineStr"/>
+      <c r="O222" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0028.mp4</t>
         </is>
@@ -19043,8 +19330,9 @@
       </c>
       <c r="K223" s="2" t="inlineStr"/>
       <c r="L223" s="2" t="inlineStr"/>
-      <c r="M223" s="6" t="inlineStr"/>
-      <c r="N223" s="2" t="inlineStr">
+      <c r="M223" s="2" t="inlineStr"/>
+      <c r="N223" s="6" t="inlineStr"/>
+      <c r="O223" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0029.mp4</t>
         </is>
@@ -19093,8 +19381,9 @@
       </c>
       <c r="K224" s="2" t="inlineStr"/>
       <c r="L224" s="2" t="inlineStr"/>
-      <c r="M224" s="6" t="inlineStr"/>
-      <c r="N224" s="2" t="inlineStr">
+      <c r="M224" s="2" t="inlineStr"/>
+      <c r="N224" s="6" t="inlineStr"/>
+      <c r="O224" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0030.mp4</t>
         </is>
@@ -19146,13 +19435,14 @@
         </is>
       </c>
       <c r="K225" s="2" t="inlineStr"/>
-      <c r="L225" s="2" t="inlineStr">
+      <c r="L225" s="2" t="inlineStr"/>
+      <c r="M225" s="2" t="inlineStr">
         <is>
           <t>video-006</t>
         </is>
       </c>
-      <c r="M225" s="6" t="inlineStr"/>
-      <c r="N225" s="2" t="inlineStr">
+      <c r="N225" s="6" t="inlineStr"/>
+      <c r="O225" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0031.mp4</t>
         </is>
@@ -19205,8 +19495,9 @@
       </c>
       <c r="K226" s="2" t="inlineStr"/>
       <c r="L226" s="2" t="inlineStr"/>
-      <c r="M226" s="6" t="inlineStr"/>
-      <c r="N226" s="2" t="inlineStr">
+      <c r="M226" s="2" t="inlineStr"/>
+      <c r="N226" s="6" t="inlineStr"/>
+      <c r="O226" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0032.mp4</t>
         </is>
@@ -19255,8 +19546,9 @@
       </c>
       <c r="K227" s="2" t="inlineStr"/>
       <c r="L227" s="2" t="inlineStr"/>
-      <c r="M227" s="6" t="inlineStr"/>
-      <c r="N227" s="2" t="inlineStr">
+      <c r="M227" s="2" t="inlineStr"/>
+      <c r="N227" s="6" t="inlineStr"/>
+      <c r="O227" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0033.mp4</t>
         </is>
@@ -19308,9 +19600,14 @@
         </is>
       </c>
       <c r="K228" s="2" t="inlineStr"/>
-      <c r="L228" s="2" t="inlineStr"/>
-      <c r="M228" s="6" t="inlineStr"/>
-      <c r="N228" s="2" t="inlineStr">
+      <c r="L228" s="2" t="inlineStr">
+        <is>
+          <t>faces — publishing permission granted 2026-09-16</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="inlineStr"/>
+      <c r="N228" s="6" t="inlineStr"/>
+      <c r="O228" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0036.mp4</t>
         </is>
@@ -19363,8 +19660,9 @@
       </c>
       <c r="K229" s="2" t="inlineStr"/>
       <c r="L229" s="2" t="inlineStr"/>
-      <c r="M229" s="6" t="inlineStr"/>
-      <c r="N229" s="2" t="inlineStr">
+      <c r="M229" s="2" t="inlineStr"/>
+      <c r="N229" s="6" t="inlineStr"/>
+      <c r="O229" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0037.mp4</t>
         </is>
@@ -19413,8 +19711,9 @@
       </c>
       <c r="K230" s="2" t="inlineStr"/>
       <c r="L230" s="2" t="inlineStr"/>
-      <c r="M230" s="6" t="inlineStr"/>
-      <c r="N230" s="2" t="inlineStr">
+      <c r="M230" s="2" t="inlineStr"/>
+      <c r="N230" s="6" t="inlineStr"/>
+      <c r="O230" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0038.mp4</t>
         </is>
@@ -19463,8 +19762,9 @@
       </c>
       <c r="K231" s="2" t="inlineStr"/>
       <c r="L231" s="2" t="inlineStr"/>
-      <c r="M231" s="6" t="inlineStr"/>
-      <c r="N231" s="2" t="inlineStr">
+      <c r="M231" s="2" t="inlineStr"/>
+      <c r="N231" s="6" t="inlineStr"/>
+      <c r="O231" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0048.mp4</t>
         </is>
@@ -19517,8 +19817,9 @@
       </c>
       <c r="K232" s="2" t="inlineStr"/>
       <c r="L232" s="2" t="inlineStr"/>
-      <c r="M232" s="6" t="inlineStr"/>
-      <c r="N232" s="2" t="inlineStr">
+      <c r="M232" s="2" t="inlineStr"/>
+      <c r="N232" s="6" t="inlineStr"/>
+      <c r="O232" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0049.mp4</t>
         </is>
@@ -19571,8 +19872,9 @@
       </c>
       <c r="K233" s="2" t="inlineStr"/>
       <c r="L233" s="2" t="inlineStr"/>
-      <c r="M233" s="6" t="inlineStr"/>
-      <c r="N233" s="2" t="inlineStr">
+      <c r="M233" s="2" t="inlineStr"/>
+      <c r="N233" s="6" t="inlineStr"/>
+      <c r="O233" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0050.mp4</t>
         </is>
@@ -19625,8 +19927,9 @@
       </c>
       <c r="K234" s="2" t="inlineStr"/>
       <c r="L234" s="2" t="inlineStr"/>
-      <c r="M234" s="6" t="inlineStr"/>
-      <c r="N234" s="2" t="inlineStr">
+      <c r="M234" s="2" t="inlineStr"/>
+      <c r="N234" s="6" t="inlineStr"/>
+      <c r="O234" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0051.mp4</t>
         </is>
@@ -19675,8 +19978,9 @@
       </c>
       <c r="K235" s="2" t="inlineStr"/>
       <c r="L235" s="2" t="inlineStr"/>
-      <c r="M235" s="6" t="inlineStr"/>
-      <c r="N235" s="2" t="inlineStr">
+      <c r="M235" s="2" t="inlineStr"/>
+      <c r="N235" s="6" t="inlineStr"/>
+      <c r="O235" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0052.mp4</t>
         </is>
@@ -19725,8 +20029,9 @@
       </c>
       <c r="K236" s="2" t="inlineStr"/>
       <c r="L236" s="2" t="inlineStr"/>
-      <c r="M236" s="6" t="inlineStr"/>
-      <c r="N236" s="2" t="inlineStr">
+      <c r="M236" s="2" t="inlineStr"/>
+      <c r="N236" s="6" t="inlineStr"/>
+      <c r="O236" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0053.mp4</t>
         </is>
@@ -19775,8 +20080,9 @@
       </c>
       <c r="K237" s="2" t="inlineStr"/>
       <c r="L237" s="2" t="inlineStr"/>
-      <c r="M237" s="6" t="inlineStr"/>
-      <c r="N237" s="2" t="inlineStr">
+      <c r="M237" s="2" t="inlineStr"/>
+      <c r="N237" s="6" t="inlineStr"/>
+      <c r="O237" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0054.mp4</t>
         </is>
@@ -19825,8 +20131,9 @@
       </c>
       <c r="K238" s="2" t="inlineStr"/>
       <c r="L238" s="2" t="inlineStr"/>
-      <c r="M238" s="6" t="inlineStr"/>
-      <c r="N238" s="2" t="inlineStr">
+      <c r="M238" s="2" t="inlineStr"/>
+      <c r="N238" s="6" t="inlineStr"/>
+      <c r="O238" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0055.mp4</t>
         </is>
@@ -19878,13 +20185,14 @@
         </is>
       </c>
       <c r="K239" s="2" t="inlineStr"/>
-      <c r="L239" s="2" t="inlineStr">
+      <c r="L239" s="2" t="inlineStr"/>
+      <c r="M239" s="2" t="inlineStr">
         <is>
           <t>video-013</t>
         </is>
       </c>
-      <c r="M239" s="6" t="inlineStr"/>
-      <c r="N239" s="2" t="inlineStr">
+      <c r="N239" s="6" t="inlineStr"/>
+      <c r="O239" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0056.mp4</t>
         </is>
@@ -19933,8 +20241,9 @@
       </c>
       <c r="K240" s="2" t="inlineStr"/>
       <c r="L240" s="2" t="inlineStr"/>
-      <c r="M240" s="6" t="inlineStr"/>
-      <c r="N240" s="2" t="inlineStr">
+      <c r="M240" s="2" t="inlineStr"/>
+      <c r="N240" s="6" t="inlineStr"/>
+      <c r="O240" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0058.mp4</t>
         </is>
@@ -19987,8 +20296,9 @@
       </c>
       <c r="K241" s="2" t="inlineStr"/>
       <c r="L241" s="2" t="inlineStr"/>
-      <c r="M241" s="6" t="inlineStr"/>
-      <c r="N241" s="2" t="inlineStr">
+      <c r="M241" s="2" t="inlineStr"/>
+      <c r="N241" s="6" t="inlineStr"/>
+      <c r="O241" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0060.mp4</t>
         </is>
@@ -20041,8 +20351,9 @@
       </c>
       <c r="K242" s="2" t="inlineStr"/>
       <c r="L242" s="2" t="inlineStr"/>
-      <c r="M242" s="6" t="inlineStr"/>
-      <c r="N242" s="2" t="inlineStr">
+      <c r="M242" s="2" t="inlineStr"/>
+      <c r="N242" s="6" t="inlineStr"/>
+      <c r="O242" s="2" t="inlineStr">
         <is>
           <t>VID-20260914-WA0062.mp4</t>
         </is>
@@ -20098,9 +20409,14 @@
           <t>Company logo intro/outro</t>
         </is>
       </c>
-      <c r="L243" s="2" t="inlineStr"/>
-      <c r="M243" s="6" t="inlineStr"/>
-      <c r="N243" s="2" t="inlineStr">
+      <c r="L243" s="2" t="inlineStr">
+        <is>
+          <t>company-owned footage including the aerial shots, confirmed 2026-09-16</t>
+        </is>
+      </c>
+      <c r="M243" s="2" t="inlineStr"/>
+      <c r="N243" s="6" t="inlineStr"/>
+      <c r="O243" s="2" t="inlineStr">
         <is>
           <t>FINAL.mp4</t>
         </is>
@@ -20157,15 +20473,16 @@
         </is>
       </c>
       <c r="L244" s="2" t="inlineStr"/>
-      <c r="M244" s="6" t="inlineStr"/>
-      <c r="N244" s="2" t="inlineStr">
+      <c r="M244" s="2" t="inlineStr"/>
+      <c r="N244" s="6" t="inlineStr"/>
+      <c r="O244" s="2" t="inlineStr">
         <is>
           <t>reel 1.mp4</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N244"/>
+  <autoFilter ref="A1:O244"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/docs/photo-triage.xlsx
+++ b/docs/photo-triage.xlsx
@@ -6681,7 +6681,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Client clearance (batch 2)</t>
+          <t>Client clearance (batches 2 and 4)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>POLICE SITE — not published; asked again 2026-09-16. faces — publishing permission granted 2026-09-16</t>
+          <t>POLICE SITE — authority clearance confirmed by the client 2026-09-17; published in the gallery, cropped to keep signage and vehicles out. faces — publishing permission granted 2026-09-16</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>POLICE SITE — not published; asked again 2026-09-16. faces — publishing permission granted 2026-09-16</t>
+          <t>POLICE SITE — not published. faces — publishing permission granted 2026-09-16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>POLICE SITE — not published; asked again 2026-09-16. faces — publishing permission granted 2026-09-16</t>
+          <t>POLICE SITE — authority clearance confirmed by the client 2026-09-17; published in the gallery, cropped to keep signage and vehicles out. faces — publishing permission granted 2026-09-16</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>POLICE SITE — not published; asked again 2026-09-16. faces — publishing permission granted 2026-09-16</t>
+          <t>POLICE SITE — not published. faces — publishing permission granted 2026-09-16</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -9142,7 +9142,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>POLICE SITE — not published; asked again 2026-09-16. faces — publishing permission granted 2026-09-16</t>
+          <t>POLICE SITE — authority clearance confirmed by the client 2026-09-17; published in the gallery, cropped to keep signage and vehicles out. faces — publishing permission granted 2026-09-16</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
@@ -9201,7 +9201,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>POLICE SITE — not published; asked again 2026-09-16. faces — publishing permission granted 2026-09-16</t>
+          <t>POLICE SITE — not published. faces — publishing permission granted 2026-09-16</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -20708,7 +20708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -21138,6 +21138,21 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>مصنع الطوب في القطامية بالأسمرات</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Brick Factory – Katameya (Al-Asmarat)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/photo-triage.xlsx
+++ b/docs/photo-triage.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Triage'!$A$1:$O$244</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Triage'!$A$1:$O$250</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5143,1164 +5143,1314 @@
       <row>197</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="781050" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="197" name="Image 197" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId197"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>198</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="781050" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="198" name="Image 198" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId198"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>199</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="781050" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="199" name="Image 199" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId199"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>200</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="781050" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="200" name="Image 200" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId200"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>201</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="781050" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="201" name="Image 201" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId201"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>202</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="781050" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="202" name="Image 202" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId202"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>203</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="197" name="Image 197" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId197"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>198</row>
+        <cNvPr id="203" name="Image 203" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId203"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>204</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="198" name="Image 198" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId198"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>199</row>
+        <cNvPr id="204" name="Image 204" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId204"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>205</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="199" name="Image 199" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId199"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>200</row>
+        <cNvPr id="205" name="Image 205" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId205"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>206</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="200" name="Image 200" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId200"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>201</row>
+        <cNvPr id="206" name="Image 206" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId206"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>207</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="201" name="Image 201" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId201"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>202</row>
+        <cNvPr id="207" name="Image 207" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId207"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>208</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="523875"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="202" name="Image 202" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId202"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>203</row>
+        <cNvPr id="208" name="Image 208" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId208"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>209</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="203" name="Image 203" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId203"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>204</row>
+        <cNvPr id="209" name="Image 209" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId209"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>210</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="523875"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="204" name="Image 204" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId204"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>205</row>
+        <cNvPr id="210" name="Image 210" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId210"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>211</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="205" name="Image 205" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId205"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>206</row>
+        <cNvPr id="211" name="Image 211" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId211"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>212</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="523875"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="206" name="Image 206" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId206"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>207</row>
+        <cNvPr id="212" name="Image 212" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId212"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>213</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="207" name="Image 207" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId207"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>208</row>
+        <cNvPr id="213" name="Image 213" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId213"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>214</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="208" name="Image 208" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId208"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>209</row>
+        <cNvPr id="214" name="Image 214" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId214"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>215</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="209" name="Image 209" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId209"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>210</row>
+        <cNvPr id="215" name="Image 215" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId215"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>216</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="210" name="Image 210" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId210"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>211</row>
+        <cNvPr id="216" name="Image 216" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId216"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>217</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="211" name="Image 211" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId211"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>212</row>
+        <cNvPr id="217" name="Image 217" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId217"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>218</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="523875"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="212" name="Image 212" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId212"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>213</row>
+        <cNvPr id="218" name="Image 218" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId218"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>219</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="213" name="Image 213" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId213"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>214</row>
+        <cNvPr id="219" name="Image 219" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId219"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>220</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="523875"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="214" name="Image 214" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId214"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>215</row>
+        <cNvPr id="220" name="Image 220" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId220"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>221</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="215" name="Image 215" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId215"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>216</row>
+        <cNvPr id="221" name="Image 221" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId221"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>222</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="216" name="Image 216" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId216"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>217</row>
+        <cNvPr id="222" name="Image 222" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId222"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>223</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="217" name="Image 217" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId217"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>218</row>
+        <cNvPr id="223" name="Image 223" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId223"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>224</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="218" name="Image 218" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId218"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>219</row>
+        <cNvPr id="224" name="Image 224" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId224"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>225</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="219" name="Image 219" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId219"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>220</row>
+        <cNvPr id="225" name="Image 225" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId225"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>226</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="220" name="Image 220" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId220"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>221</row>
+        <cNvPr id="226" name="Image 226" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId226"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>227</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="523875"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="221" name="Image 221" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId221"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>222</row>
+        <cNvPr id="227" name="Image 227" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId227"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>228</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="523875"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="222" name="Image 222" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId222"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>223</row>
+        <cNvPr id="228" name="Image 228" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId228"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>229</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="223" name="Image 223" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId223"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>224</row>
+        <cNvPr id="229" name="Image 229" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId229"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>230</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="523875"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="224" name="Image 224" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId224"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>225</row>
+        <cNvPr id="230" name="Image 230" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId230"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>231</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="225" name="Image 225" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId225"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>226</row>
+        <cNvPr id="231" name="Image 231" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId231"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>232</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="226" name="Image 226" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId226"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>227</row>
+        <cNvPr id="232" name="Image 232" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId232"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>233</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="227" name="Image 227" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId227"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>228</row>
+        <cNvPr id="233" name="Image 233" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId233"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>234</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="228" name="Image 228" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId228"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>229</row>
+        <cNvPr id="234" name="Image 234" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId234"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>235</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="229" name="Image 229" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId229"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>230</row>
+        <cNvPr id="235" name="Image 235" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId235"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>236</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="230" name="Image 230" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId230"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>231</row>
+        <cNvPr id="236" name="Image 236" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId236"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>237</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="231" name="Image 231" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId231"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>232</row>
+        <cNvPr id="237" name="Image 237" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId237"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>238</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="232" name="Image 232" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId232"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>233</row>
+        <cNvPr id="238" name="Image 238" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId238"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>239</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="523875"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="233" name="Image 233" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId233"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>234</row>
+        <cNvPr id="239" name="Image 239" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId239"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>240</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="234" name="Image 234" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId234"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>235</row>
+        <cNvPr id="240" name="Image 240" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId240"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>241</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="523875"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="235" name="Image 235" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId235"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>236</row>
+        <cNvPr id="241" name="Image 241" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId241"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>242</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="523875"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="236" name="Image 236" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId236"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>237</row>
+        <cNvPr id="242" name="Image 242" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId242"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>243</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="523875"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="237" name="Image 237" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId237"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>238</row>
+        <cNvPr id="243" name="Image 243" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId243"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>244</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="238" name="Image 238" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId238"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>239</row>
+        <cNvPr id="244" name="Image 244" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId244"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>245</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="239" name="Image 239" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId239"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>240</row>
+        <cNvPr id="245" name="Image 245" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId245"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>246</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="523875"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="240" name="Image 240" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId240"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>241</row>
+        <cNvPr id="246" name="Image 246" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId246"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>247</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="523875"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="241" name="Image 241" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId241"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>242</row>
+        <cNvPr id="247" name="Image 247" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId247"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>248</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="523875"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="242" name="Image 242" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId242"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>243</row>
+        <cNvPr id="248" name="Image 248" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId248"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>249</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1819275" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="243" name="Image 243" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId243"/>
+        <cNvPr id="249" name="Image 249" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId249"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -6603,7 +6753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O244"/>
+  <dimension ref="A1:O250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -17943,37 +18093,41 @@
     <row r="198" ht="88" customHeight="1">
       <c r="A198" s="2" t="inlineStr"/>
       <c r="B198" s="3" t="n">
-        <v>1</v>
+        <v>197</v>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>تجوّل داخل مبنى خرساني قيد الإنشاء: أعمدة وسلالم وحديد تسليح</t>
+          <t>جريدر يسوّي طبقة تربة حمراء بجانب طريق قائم ونخيل في الخلفية</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Brick factories — مصانع الطوب</t>
+          <t>Development &amp; maintenance — التطوير والصيانة</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>building works</t>
-        </is>
-      </c>
-      <c r="G198" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H198" s="2" t="inlineStr"/>
+          <t>earthworks / grading; equipment</t>
+        </is>
+      </c>
+      <c r="G198" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>Sharp action shot of the grader at work beside the live carriageway; the operator is only a silhouette. Portrait: the 4:3 crop is 960x720.</t>
+        </is>
+      </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>474×850 portrait · 7.0 s · 30 fps · H264 · 1.1 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
+          <t>960×1280 portrait · 207 KB · WhatsApp-compressed (≤1600 px, JPEG q≈75, no EXIF) · sharpness sharp (1761) · 1.6% highlights clipped</t>
         </is>
       </c>
       <c r="J198" s="3" t="inlineStr">
@@ -17981,54 +18135,60 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t>CAT maker badge on the grader</t>
+        </is>
+      </c>
       <c r="L198" s="2" t="inlineStr"/>
       <c r="M198" s="2" t="inlineStr"/>
-      <c r="N198" s="6" t="inlineStr"/>
+      <c r="N198" s="6" t="n">
+        <v>30</v>
+      </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
-          <t>VID-20260913-WA0208.mp4</t>
+          <t>batch2/WhatsApp Image 2026-09-18 at 2.04.49 PM.jpeg</t>
         </is>
       </c>
     </row>
     <row r="199" ht="88" customHeight="1">
       <c r="A199" s="2" t="inlineStr"/>
       <c r="B199" s="3" t="n">
-        <v>2</v>
+        <v>198</v>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>لقطة قصيرة من داخل سيارة لشاحنات وشخص (لوحة القيادة ظاهرة)</t>
+          <t>سيارة مياه ترش طبقة التربة قبل الدمك ونخيل على الجانب</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
+          <t>Development &amp; maintenance — التطوير والصيانة</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>trucks</t>
-        </is>
-      </c>
-      <c r="G199" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>earthworks / grading; trucks</t>
+        </is>
+      </c>
+      <c r="G199" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>Filmed through a windscreen with the dashboard in frame; 3 s.</t>
+          <t>Watering the subgrade; no readable plate.</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>476×856 portrait · 2.7 s · 30 fps · H264 · 0.5 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static · view: ground (vehicle) · daylight</t>
+          <t>960×1280 portrait · 152 KB · WhatsApp-compressed (≤1600 px, JPEG q≈75, no EXIF) · sharpness sharp (1009) · 9.8% highlights clipped</t>
         </is>
       </c>
       <c r="J199" s="3" t="inlineStr">
@@ -18036,50 +18196,60 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>Faded, illegible paint on the tank</t>
+        </is>
+      </c>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr"/>
-      <c r="N199" s="6" t="inlineStr"/>
+      <c r="N199" s="6" t="n">
+        <v>30</v>
+      </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
-          <t>VID-20260913-WA0209.mp4</t>
+          <t>batch2/WhatsApp Image 2026-09-18 at 2.05.02 PM.jpeg</t>
         </is>
       </c>
     </row>
     <row r="200" ht="88" customHeight="1">
       <c r="A200" s="2" t="inlineStr"/>
       <c r="B200" s="3" t="n">
-        <v>3</v>
+        <v>199</v>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>جريدر ومسّاح بقامة مساحية على طريق ممهّد</t>
+          <t>مقطورة قلاب تفرّغ تربة وسط الغبار تحت سماء بسحب</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
+          <t>Development &amp; maintenance — التطوير والصيانة</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>earthworks; surveying; equipment</t>
-        </is>
-      </c>
-      <c r="G200" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H200" s="2" t="inlineStr"/>
+          <t>earthworks / grading; trucks</t>
+        </is>
+      </c>
+      <c r="G200" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>Most dramatic frame of the batch. The decals are legible but are not company branding.</t>
+        </is>
+      </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>476×848 portrait · 8.8 s · 30 fps · H264 · 1.8 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static · view: ground · daylight</t>
+          <t>960×1280 portrait · 195 KB · WhatsApp-compressed (≤1600 px, JPEG q≈75, no EXIF) · sharpness sharp (1219)</t>
         </is>
       </c>
       <c r="J200" s="3" t="inlineStr">
@@ -18087,39 +18257,45 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>Tailgate decals (a religious phrase), trailer maker marks, a fleet number on the second trailer</t>
+        </is>
+      </c>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr"/>
-      <c r="N200" s="6" t="inlineStr"/>
+      <c r="N200" s="6" t="n">
+        <v>30</v>
+      </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
-          <t>VID-20260913-WA0212.mp4</t>
+          <t>batch2/WhatsApp Image 2026-09-18 at 2.05.03 PM.jpeg</t>
         </is>
       </c>
     </row>
     <row r="201" ht="88" customHeight="1">
       <c r="A201" s="2" t="inlineStr"/>
       <c r="B201" s="3" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>تجوّل داخل منشأ معدني (هنجر) قيد التركيب</t>
+          <t>جريدر عند حافة الكادر يسوّي تربة رملية تحت سماء صافية</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Brick factories — مصانع الطوب</t>
+          <t>Development &amp; maintenance — التطوير والصيانة</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>steel structure</t>
+          <t>earthworks / grading; equipment</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
@@ -18129,12 +18305,12 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>Sun flares while panning.</t>
+          <t>The machine is cut off by the left edge; the operator is not identifiable.</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 8.9 s · 30 fps · H264 · 1.4 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld pan · view: ground · daylight</t>
+          <t>960×1280 portrait · 121 KB · WhatsApp-compressed (≤1600 px, JPEG q≈75, no EXIF) · sharpness acceptable (539) · 9.7% highlights clipped</t>
         </is>
       </c>
       <c r="J201" s="3" t="inlineStr">
@@ -18145,36 +18321,38 @@
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr"/>
       <c r="M201" s="2" t="inlineStr"/>
-      <c r="N201" s="6" t="inlineStr"/>
+      <c r="N201" s="6" t="n">
+        <v>30</v>
+      </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
-          <t>VID-20260913-WA0214.mp4</t>
+          <t>batch2/WhatsApp Image 2026-09-18 at 2.05.03 PM (1).jpeg</t>
         </is>
       </c>
     </row>
     <row r="202" ht="88" customHeight="1">
       <c r="A202" s="2" t="inlineStr"/>
       <c r="B202" s="3" t="n">
-        <v>5</v>
+        <v>201</v>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>نسخة مطابقة من فيديو 004</t>
+          <t>طبقة تربة ممهدة وقت الغروب بجانب طريق قائم وظل المصوّر في المقدمة</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>Brick factories — مصانع الطوب</t>
+          <t>Development &amp; maintenance — التطوير والصيانة</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>steel structure</t>
+          <t>earthworks / grading</t>
         </is>
       </c>
       <c r="G202" s="7" t="inlineStr">
@@ -18184,12 +18362,12 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>Exact duplicate of video 004.</t>
+          <t>The photographer's long shadow crosses the foreground and stays in any 4:3 crop; 202 shows the same stretch better.</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 8.9 s · 30 fps · H264 · 1.4 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld pan · view: ground · daylight</t>
+          <t>960×1280 portrait · 130 KB · WhatsApp-compressed (≤1600 px, JPEG q≈75, no EXIF) · sharpness acceptable (564)</t>
         </is>
       </c>
       <c r="J202" s="3" t="inlineStr">
@@ -18199,41 +18377,39 @@
       </c>
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr"/>
-      <c r="M202" s="2" t="inlineStr">
-        <is>
-          <t>video-004</t>
-        </is>
-      </c>
-      <c r="N202" s="6" t="inlineStr"/>
+      <c r="M202" s="2" t="inlineStr"/>
+      <c r="N202" s="6" t="n">
+        <v>30</v>
+      </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
-          <t>VID-20260913-WA0214_1.mp4</t>
+          <t>batch2/WhatsApp Image 2026-09-18 at 2.05.03 PM (2).jpeg</t>
         </is>
       </c>
     </row>
     <row r="203" ht="88" customHeight="1">
       <c r="A203" s="2" t="inlineStr"/>
       <c r="B203" s="3" t="n">
-        <v>6</v>
+        <v>202</v>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>جريدر ومسّاح على طريق ممهّد (أفقي)</t>
+          <t>ممر الطريق بعد التسوية ومعدات على بعد ومسّاح يمسك قامة الميزانية</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
+          <t>Development &amp; maintenance — التطوير والصيانة</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>earthworks; surveying; equipment</t>
+          <t>earthworks / grading; surveying; workers</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
@@ -18243,33 +18419,35 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>Zooms during the clip.</t>
+          <t>The surveyor at the right edge is in profile (face partly visible). The published 760x570 crop stops at x=760 and leaves him out, so there is no permission question.</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>848×478 landscape · 14.5 s · 30 fps · H264 · 2.8 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static with zoom · view: ground · daylight</t>
-        </is>
-      </c>
-      <c r="J203" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>960×1280 portrait · 172 KB · WhatsApp-compressed (≤1600 px, JPEG q≈75, no EXIF) · sharpness sharp (1440) · 2.3% highlights clipped</t>
+        </is>
+      </c>
+      <c r="J203" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr"/>
       <c r="M203" s="2" t="inlineStr"/>
-      <c r="N203" s="6" t="inlineStr"/>
+      <c r="N203" s="6" t="n">
+        <v>30</v>
+      </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
-          <t>VID-20260913-WA0215.mp4</t>
+          <t>batch2/WhatsApp Image 2026-09-18 at 2.05.04 PM.jpeg</t>
         </is>
       </c>
     </row>
     <row r="204" ht="88" customHeight="1">
       <c r="A204" s="2" t="inlineStr"/>
       <c r="B204" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
@@ -18278,17 +18456,17 @@
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>تبطين ميول خرسانية بألواح متعرّجة — تصوير متحرك</t>
+          <t>تجوّل داخل مبنى خرساني قيد الإنشاء: أعمدة وسلالم وحديد تسليح</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
+          <t>Brick factories — مصانع الطوب</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>concrete slopes</t>
+          <t>building works</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
@@ -18296,14 +18474,10 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H204" s="2" t="inlineStr">
-        <is>
-          <t>Some overexposed frames.</t>
-        </is>
-      </c>
+      <c r="H204" s="2" t="inlineStr"/>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 41.6 s · 30 fps · H264 · 7.5 MB · audio: aac mono · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
+          <t>474×850 portrait · 7.0 s · 30 fps · H264 · 1.1 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
         </is>
       </c>
       <c r="J204" s="3" t="inlineStr">
@@ -18317,14 +18491,14 @@
       <c r="N204" s="6" t="inlineStr"/>
       <c r="O204" s="2" t="inlineStr">
         <is>
-          <t>VID-20260913-WA0216.mp4</t>
+          <t>VID-20260913-WA0208.mp4</t>
         </is>
       </c>
     </row>
     <row r="205" ht="88" customHeight="1">
       <c r="A205" s="2" t="inlineStr"/>
       <c r="B205" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
@@ -18333,7 +18507,7 @@
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>قيادة على طريق ممهّد طويل وسط الصحراء</t>
+          <t>لقطة قصيرة من داخل سيارة لشاحنات وشخص (لوحة القيادة ظاهرة)</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -18343,22 +18517,22 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>earthworks / grading</t>
-        </is>
-      </c>
-      <c r="G205" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>trucks</t>
+        </is>
+      </c>
+      <c r="G205" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>Long (2.5 min), steady forward motion.</t>
+          <t>Filmed through a windscreen with the dashboard in frame; 3 s.</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>848×478 landscape · 147.5 s · 30 fps · H264 · 19.6 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: steady, vehicle-mounted · view: ground (vehicle) · daylight</t>
+          <t>476×856 portrait · 2.7 s · 30 fps · H264 · 0.5 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static · view: ground (vehicle) · daylight</t>
         </is>
       </c>
       <c r="J205" s="3" t="inlineStr">
@@ -18372,14 +18546,14 @@
       <c r="N205" s="6" t="inlineStr"/>
       <c r="O205" s="2" t="inlineStr">
         <is>
-          <t>VID-20260913-WA0232.mp4</t>
+          <t>VID-20260913-WA0209.mp4</t>
         </is>
       </c>
     </row>
     <row r="206" ht="88" customHeight="1">
       <c r="A206" s="2" t="inlineStr"/>
       <c r="B206" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
@@ -18388,7 +18562,7 @@
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>ميول خرسانية بنقشة مثلثات — تصوير متحرك</t>
+          <t>جريدر ومسّاح بقامة مساحية على طريق ممهّد</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -18398,7 +18572,7 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>concrete slopes</t>
+          <t>earthworks; surveying; equipment</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
@@ -18409,7 +18583,7 @@
       <c r="H206" s="2" t="inlineStr"/>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 79.0 s · 30 fps · H264 · 14.3 MB · audio: aac mono · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
+          <t>476×848 portrait · 8.8 s · 30 fps · H264 · 1.8 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static · view: ground · daylight</t>
         </is>
       </c>
       <c r="J206" s="3" t="inlineStr">
@@ -18423,14 +18597,14 @@
       <c r="N206" s="6" t="inlineStr"/>
       <c r="O206" s="2" t="inlineStr">
         <is>
-          <t>VID-20260913-WA0233.mp4</t>
+          <t>VID-20260913-WA0212.mp4</t>
         </is>
       </c>
     </row>
     <row r="207" ht="88" customHeight="1">
       <c r="A207" s="2" t="inlineStr"/>
       <c r="B207" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
@@ -18439,17 +18613,17 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>قيادة على طريق أسفلتي جديد بخطوط أرضية صفراء وبيضاء</t>
+          <t>تجوّل داخل منشأ معدني (هنجر) قيد التركيب</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
+          <t>Brick factories — مصانع الطوب</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>asphalt; road marking</t>
+          <t>steel structure</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
@@ -18459,12 +18633,12 @@
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>Only footage of finished asphalt with fresh markings.</t>
+          <t>Sun flares while panning.</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>848×478 landscape · 10.5 s · 30 fps · H264 · 1.5 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: steady, vehicle-mounted · view: ground (vehicle) · daylight</t>
+          <t>478×850 portrait · 8.9 s · 30 fps · H264 · 1.4 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld pan · view: ground · daylight</t>
         </is>
       </c>
       <c r="J207" s="3" t="inlineStr">
@@ -18478,14 +18652,14 @@
       <c r="N207" s="6" t="inlineStr"/>
       <c r="O207" s="2" t="inlineStr">
         <is>
-          <t>VID-20260913-WA0234.mp4</t>
+          <t>VID-20260913-WA0214.mp4</t>
         </is>
       </c>
     </row>
     <row r="208" ht="88" customHeight="1">
       <c r="A208" s="2" t="inlineStr"/>
       <c r="B208" s="3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
@@ -18494,28 +18668,32 @@
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>أعمال ميول على منحدرات بجوار جبال مع خلاطات</t>
+          <t>نسخة مطابقة من فيديو 004</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
+          <t>Brick factories — مصانع الطوب</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>concrete slopes; equipment</t>
-        </is>
-      </c>
-      <c r="G208" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H208" s="2" t="inlineStr"/>
+          <t>steel structure</t>
+        </is>
+      </c>
+      <c r="G208" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of video 004.</t>
+        </is>
+      </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>480×864 portrait · 30.7 s · 30 fps · H264 · 5.2 MB · audio: aac mono · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
+          <t>478×850 portrait · 8.9 s · 30 fps · H264 · 1.4 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld pan · view: ground · daylight</t>
         </is>
       </c>
       <c r="J208" s="3" t="inlineStr">
@@ -18525,18 +18703,22 @@
       </c>
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="2" t="inlineStr"/>
-      <c r="M208" s="2" t="inlineStr"/>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>video-004</t>
+        </is>
+      </c>
       <c r="N208" s="6" t="inlineStr"/>
       <c r="O208" s="2" t="inlineStr">
         <is>
-          <t>VID-20260913-WA0235.mp4</t>
+          <t>VID-20260913-WA0214_1.mp4</t>
         </is>
       </c>
     </row>
     <row r="209" ht="88" customHeight="1">
       <c r="A209" s="2" t="inlineStr"/>
       <c r="B209" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
@@ -18545,7 +18727,7 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>لودر يقترب محمّلًا بالتربة</t>
+          <t>جريدر ومسّاح على طريق ممهّد (أفقي)</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -18555,7 +18737,7 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>equipment; earthworks</t>
+          <t>earthworks; surveying; equipment</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
@@ -18563,10 +18745,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>Zooms during the clip.</t>
+        </is>
+      </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 13.1 s · 30 fps · H264 · 2.8 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static · view: ground · daylight</t>
+          <t>848×478 landscape · 14.5 s · 30 fps · H264 · 2.8 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static with zoom · view: ground · daylight</t>
         </is>
       </c>
       <c r="J209" s="3" t="inlineStr">
@@ -18580,14 +18766,14 @@
       <c r="N209" s="6" t="inlineStr"/>
       <c r="O209" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0000.mp4</t>
+          <t>VID-20260913-WA0215.mp4</t>
         </is>
       </c>
     </row>
     <row r="210" ht="88" customHeight="1">
       <c r="A210" s="2" t="inlineStr"/>
       <c r="B210" s="3" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
@@ -18596,7 +18782,7 @@
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>هراس وجريدرات تعمل على طبقة ترابية</t>
+          <t>تبطين ميول خرسانية بألواح متعرّجة — تصوير متحرك</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -18606,7 +18792,7 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>earthworks; compaction; equipment</t>
+          <t>concrete slopes</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
@@ -18614,10 +18800,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>Some overexposed frames.</t>
+        </is>
+      </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 23.3 s · 30 fps · H264 · 5.2 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
+          <t>478×850 portrait · 41.6 s · 30 fps · H264 · 7.5 MB · audio: aac mono · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
         </is>
       </c>
       <c r="J210" s="3" t="inlineStr">
@@ -18631,14 +18821,14 @@
       <c r="N210" s="6" t="inlineStr"/>
       <c r="O210" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0004.mp4</t>
+          <t>VID-20260913-WA0216.mp4</t>
         </is>
       </c>
     </row>
     <row r="211" ht="88" customHeight="1">
       <c r="A211" s="2" t="inlineStr"/>
       <c r="B211" s="3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
@@ -18647,7 +18837,7 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>جريدر ومسّاح (قريب جدًا من فيديو 003)</t>
+          <t>قيادة على طريق ممهّد طويل وسط الصحراء</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -18657,22 +18847,22 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>earthworks; surveying</t>
-        </is>
-      </c>
-      <c r="G211" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>earthworks / grading</t>
+        </is>
+      </c>
+      <c r="G211" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>Near-duplicate of video 003.</t>
+          <t>Long (2.5 min), steady forward motion.</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 8.8 s · 30 fps · H264 · 2.0 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static · view: ground · daylight</t>
+          <t>848×478 landscape · 147.5 s · 30 fps · H264 · 19.6 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: steady, vehicle-mounted · view: ground (vehicle) · daylight</t>
         </is>
       </c>
       <c r="J211" s="3" t="inlineStr">
@@ -18682,22 +18872,18 @@
       </c>
       <c r="K211" s="2" t="inlineStr"/>
       <c r="L211" s="2" t="inlineStr"/>
-      <c r="M211" s="2" t="inlineStr">
-        <is>
-          <t>video-003</t>
-        </is>
-      </c>
+      <c r="M211" s="2" t="inlineStr"/>
       <c r="N211" s="6" t="inlineStr"/>
       <c r="O211" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0005.mp4</t>
+          <t>VID-20260913-WA0232.mp4</t>
         </is>
       </c>
     </row>
     <row r="212" ht="88" customHeight="1">
       <c r="A212" s="2" t="inlineStr"/>
       <c r="B212" s="3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
@@ -18706,7 +18892,7 @@
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>جريدر يقترب من الكاميرا على تربة حمراء</t>
+          <t>ميول خرسانية بنقشة مثلثات — تصوير متحرك</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -18716,7 +18902,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>equipment</t>
+          <t>concrete slopes</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
@@ -18727,7 +18913,7 @@
       <c r="H212" s="2" t="inlineStr"/>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 8.6 s · 30 fps · H264 · 1.9 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static · view: ground · daylight</t>
+          <t>478×850 portrait · 79.0 s · 30 fps · H264 · 14.3 MB · audio: aac mono · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
         </is>
       </c>
       <c r="J212" s="3" t="inlineStr">
@@ -18741,14 +18927,14 @@
       <c r="N212" s="6" t="inlineStr"/>
       <c r="O212" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0006.mp4</t>
+          <t>VID-20260913-WA0233.mp4</t>
         </is>
       </c>
     </row>
     <row r="213" ht="88" customHeight="1">
       <c r="A213" s="2" t="inlineStr"/>
       <c r="B213" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
@@ -18757,7 +18943,7 @@
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>مسّاح بجهاز ميزان مع جريدر — شعار شركة أخرى على السترة</t>
+          <t>قيادة على طريق أسفلتي جديد بخطوط أرضية صفراء وبيضاء</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -18767,51 +18953,43 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>surveying; workers</t>
-        </is>
-      </c>
-      <c r="G213" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>asphalt; road marking</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>Clear face plus another company's logo on the vest (possibly the main contractor): confirm before any use.</t>
+          <t>Only footage of finished asphalt with fresh markings.</t>
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>848×478 landscape · 25.4 s · 30 fps · H264 · 5.7 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
-        </is>
-      </c>
-      <c r="J213" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K213" s="2" t="inlineStr">
-        <is>
-          <t>Third-party logo "SG … Group" on the vest</t>
-        </is>
-      </c>
-      <c r="L213" s="2" t="inlineStr">
-        <is>
-          <t>third-party "SG" logo — partner contractor, cleared to publish 2026-09-16</t>
-        </is>
-      </c>
+          <t>848×478 landscape · 10.5 s · 30 fps · H264 · 1.5 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: steady, vehicle-mounted · view: ground (vehicle) · daylight</t>
+        </is>
+      </c>
+      <c r="J213" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr"/>
       <c r="M213" s="2" t="inlineStr"/>
       <c r="N213" s="6" t="inlineStr"/>
       <c r="O213" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0007.mp4</t>
+          <t>VID-20260913-WA0234.mp4</t>
         </is>
       </c>
     </row>
     <row r="214" ht="88" customHeight="1">
       <c r="A214" s="2" t="inlineStr"/>
       <c r="B214" s="3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
@@ -18820,7 +18998,7 @@
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>لودر بمخالب نزع مع الشمس داخل الكادر</t>
+          <t>أعمال ميول على منحدرات بجوار جبال مع خلاطات</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -18830,22 +19008,18 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="G214" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H214" s="2" t="inlineStr">
-        <is>
-          <t>Sun glare throughout.</t>
-        </is>
-      </c>
+          <t>concrete slopes; equipment</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr"/>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 8.7 s · 30 fps · H264 · 1.9 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static · view: ground · daylight</t>
+          <t>480×864 portrait · 30.7 s · 30 fps · H264 · 5.2 MB · audio: aac mono · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
         </is>
       </c>
       <c r="J214" s="3" t="inlineStr">
@@ -18859,14 +19033,14 @@
       <c r="N214" s="6" t="inlineStr"/>
       <c r="O214" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0008.mp4</t>
+          <t>VID-20260913-WA0235.mp4</t>
         </is>
       </c>
     </row>
     <row r="215" ht="88" customHeight="1">
       <c r="A215" s="2" t="inlineStr"/>
       <c r="B215" s="3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
@@ -18875,7 +19049,7 @@
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>حفار يحفر تلًا صخريًا مع جبال في الخلفية</t>
+          <t>لودر يقترب محمّلًا بالتربة</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -18885,7 +19059,7 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>excavation; equipment</t>
+          <t>equipment; earthworks</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
@@ -18896,7 +19070,7 @@
       <c r="H215" s="2" t="inlineStr"/>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>848×480 landscape · 24.8 s · 29 fps · H264 · 5.1 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
+          <t>478×850 portrait · 13.1 s · 30 fps · H264 · 2.8 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static · view: ground · daylight</t>
         </is>
       </c>
       <c r="J215" s="3" t="inlineStr">
@@ -18910,14 +19084,14 @@
       <c r="N215" s="6" t="inlineStr"/>
       <c r="O215" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0020.mp4</t>
+          <t>VID-20260914-WA0000.mp4</t>
         </is>
       </c>
     </row>
     <row r="216" ht="88" customHeight="1">
       <c r="A216" s="2" t="inlineStr"/>
       <c r="B216" s="3" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
@@ -18926,17 +19100,17 @@
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>أعمال أساسات: حديد تسليح وشدات داخل هنجر</t>
+          <t>هراس وجريدرات تعمل على طبقة ترابية</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>Brick factories — مصانع الطوب</t>
+          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>foundations; rebar</t>
+          <t>earthworks; compaction; equipment</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -18947,7 +19121,7 @@
       <c r="H216" s="2" t="inlineStr"/>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>474×850 portrait · 24.9 s · 30 fps · H264 · 3.7 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
+          <t>478×850 portrait · 23.3 s · 30 fps · H264 · 5.2 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
         </is>
       </c>
       <c r="J216" s="3" t="inlineStr">
@@ -18961,14 +19135,14 @@
       <c r="N216" s="6" t="inlineStr"/>
       <c r="O216" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0021.mp4</t>
+          <t>VID-20260914-WA0004.mp4</t>
         </is>
       </c>
     </row>
     <row r="217" ht="88" customHeight="1">
       <c r="A217" s="2" t="inlineStr"/>
       <c r="B217" s="3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
@@ -18977,7 +19151,7 @@
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>هراس وجريدر على تربة حمراء تحت سماء صافية</t>
+          <t>جريدر ومسّاح (قريب جدًا من فيديو 003)</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -18987,18 +19161,22 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>earthworks; compaction; equipment</t>
-        </is>
-      </c>
-      <c r="G217" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H217" s="2" t="inlineStr"/>
+          <t>earthworks; surveying</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>Near-duplicate of video 003.</t>
+        </is>
+      </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 14.2 s · 30 fps · H264 · 3.0 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
+          <t>478×850 portrait · 8.8 s · 30 fps · H264 · 2.0 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static · view: ground · daylight</t>
         </is>
       </c>
       <c r="J217" s="3" t="inlineStr">
@@ -19008,18 +19186,22 @@
       </c>
       <c r="K217" s="2" t="inlineStr"/>
       <c r="L217" s="2" t="inlineStr"/>
-      <c r="M217" s="2" t="inlineStr"/>
+      <c r="M217" s="2" t="inlineStr">
+        <is>
+          <t>video-003</t>
+        </is>
+      </c>
       <c r="N217" s="6" t="inlineStr"/>
       <c r="O217" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0022.mp4</t>
+          <t>VID-20260914-WA0005.mp4</t>
         </is>
       </c>
     </row>
     <row r="218" ht="88" customHeight="1">
       <c r="A218" s="2" t="inlineStr"/>
       <c r="B218" s="3" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
@@ -19028,7 +19210,7 @@
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>لودر كاتربيلر بلقطات قريبة مهتزة</t>
+          <t>جريدر يقترب من الكاميرا على تربة حمراء</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -19041,19 +19223,15 @@
           <t>equipment</t>
         </is>
       </c>
-      <c r="G218" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H218" s="2" t="inlineStr">
-        <is>
-          <t>Very shaky close-ups.</t>
-        </is>
-      </c>
+      <c r="G218" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr"/>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 20.7 s · 30 fps · H264 · 4.6 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: shaky handheld · view: ground · daylight</t>
+          <t>478×850 portrait · 8.6 s · 30 fps · H264 · 1.9 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static · view: ground · daylight</t>
         </is>
       </c>
       <c r="J218" s="3" t="inlineStr">
@@ -19067,14 +19245,14 @@
       <c r="N218" s="6" t="inlineStr"/>
       <c r="O218" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0024.mp4</t>
+          <t>VID-20260914-WA0006.mp4</t>
         </is>
       </c>
     </row>
     <row r="219" ht="88" customHeight="1">
       <c r="A219" s="2" t="inlineStr"/>
       <c r="B219" s="3" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
@@ -19083,7 +19261,7 @@
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>جريدر كاتربيلر يدور على رمال</t>
+          <t>مسّاح بجهاز ميزان مع جريدر — شعار شركة أخرى على السترة</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -19093,39 +19271,51 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>equipment; earthworks</t>
-        </is>
-      </c>
-      <c r="G219" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H219" s="2" t="inlineStr"/>
+          <t>surveying; workers</t>
+        </is>
+      </c>
+      <c r="G219" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>Clear face plus another company's logo on the vest (possibly the main contractor): confirm before any use.</t>
+        </is>
+      </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 14.6 s · 30 fps · H264 · 3.2 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
-        </is>
-      </c>
-      <c r="J219" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K219" s="2" t="inlineStr"/>
-      <c r="L219" s="2" t="inlineStr"/>
+          <t>848×478 landscape · 25.4 s · 30 fps · H264 · 5.7 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
+        </is>
+      </c>
+      <c r="J219" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K219" s="2" t="inlineStr">
+        <is>
+          <t>Third-party logo "SG … Group" on the vest</t>
+        </is>
+      </c>
+      <c r="L219" s="2" t="inlineStr">
+        <is>
+          <t>third-party "SG" logo — partner contractor, cleared to publish 2026-09-16</t>
+        </is>
+      </c>
       <c r="M219" s="2" t="inlineStr"/>
       <c r="N219" s="6" t="inlineStr"/>
       <c r="O219" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0025.mp4</t>
+          <t>VID-20260914-WA0007.mp4</t>
         </is>
       </c>
     </row>
     <row r="220" ht="88" customHeight="1">
       <c r="A220" s="2" t="inlineStr"/>
       <c r="B220" s="3" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
@@ -19134,7 +19324,7 @@
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>تسوية ساتر ترابي أحمر بالجريدر أثناء المشي</t>
+          <t>لودر بمخالب نزع مع الشمس داخل الكادر</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -19144,22 +19334,22 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>earthworks; equipment</t>
-        </is>
-      </c>
-      <c r="G220" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="G220" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>Tilted at times.</t>
+          <t>Sun glare throughout.</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 30.9 s · 30 fps · H264 · 4.0 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
+          <t>478×850 portrait · 8.7 s · 30 fps · H264 · 1.9 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static · view: ground · daylight</t>
         </is>
       </c>
       <c r="J220" s="3" t="inlineStr">
@@ -19173,14 +19363,14 @@
       <c r="N220" s="6" t="inlineStr"/>
       <c r="O220" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0026.mp4</t>
+          <t>VID-20260914-WA0008.mp4</t>
         </is>
       </c>
     </row>
     <row r="221" ht="88" customHeight="1">
       <c r="A221" s="2" t="inlineStr"/>
       <c r="B221" s="3" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
@@ -19189,17 +19379,17 @@
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>هنجر معدني بسقالات وأعمدة</t>
+          <t>حفار يحفر تلًا صخريًا مع جبال في الخلفية</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>Brick factories — مصانع الطوب</t>
+          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>steel structure</t>
+          <t>excavation; equipment</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
@@ -19207,14 +19397,10 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H221" s="2" t="inlineStr">
-        <is>
-          <t>Similar subject to video 004.</t>
-        </is>
-      </c>
+      <c r="H221" s="2" t="inlineStr"/>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>474×850 portrait · 11.8 s · 30 fps · H264 · 1.9 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld pan · view: ground · daylight</t>
+          <t>848×480 landscape · 24.8 s · 29 fps · H264 · 5.1 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
         </is>
       </c>
       <c r="J221" s="3" t="inlineStr">
@@ -19228,14 +19414,14 @@
       <c r="N221" s="6" t="inlineStr"/>
       <c r="O221" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0027.mp4</t>
+          <t>VID-20260914-WA0020.mp4</t>
         </is>
       </c>
     </row>
     <row r="222" ht="88" customHeight="1">
       <c r="A222" s="2" t="inlineStr"/>
       <c r="B222" s="3" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
@@ -19244,17 +19430,17 @@
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>لقطات سينمائية للودر كاتربيلر 966E</t>
+          <t>أعمال أساسات: حديد تسليح وشدات داخل هنجر</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
+          <t>Brick factories — مصانع الطوب</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>equipment</t>
+          <t>foundations; rebar</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
@@ -19262,14 +19448,10 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H222" s="2" t="inlineStr">
-        <is>
-          <t>One out-of-focus section; likely raw footage for the company edit.</t>
-        </is>
-      </c>
+      <c r="H222" s="2" t="inlineStr"/>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>848×478 landscape · 21.0 s · 30 fps · H264 · 4.7 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: stabilised, cinematic · view: ground · daylight</t>
+          <t>474×850 portrait · 24.9 s · 30 fps · H264 · 3.7 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
         </is>
       </c>
       <c r="J222" s="3" t="inlineStr">
@@ -19283,14 +19465,14 @@
       <c r="N222" s="6" t="inlineStr"/>
       <c r="O222" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0028.mp4</t>
+          <t>VID-20260914-WA0021.mp4</t>
         </is>
       </c>
     </row>
     <row r="223" ht="88" customHeight="1">
       <c r="A223" s="2" t="inlineStr"/>
       <c r="B223" s="3" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
@@ -19299,7 +19481,7 @@
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>جريدر بزاوية منخفضة سينمائية</t>
+          <t>هراس وجريدر على تربة حمراء تحت سماء صافية</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -19309,7 +19491,7 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>equipment</t>
+          <t>earthworks; compaction; equipment</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -19320,7 +19502,7 @@
       <c r="H223" s="2" t="inlineStr"/>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>848×478 landscape · 12.7 s · 30 fps · H264 · 2.8 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: stabilised, cinematic · view: ground · daylight</t>
+          <t>478×850 portrait · 14.2 s · 30 fps · H264 · 3.0 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
         </is>
       </c>
       <c r="J223" s="3" t="inlineStr">
@@ -19334,14 +19516,14 @@
       <c r="N223" s="6" t="inlineStr"/>
       <c r="O223" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0029.mp4</t>
+          <t>VID-20260914-WA0022.mp4</t>
         </is>
       </c>
     </row>
     <row r="224" ht="88" customHeight="1">
       <c r="A224" s="2" t="inlineStr"/>
       <c r="B224" s="3" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
@@ -19350,7 +19532,7 @@
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>لودر يدفع رملًا على منحدر</t>
+          <t>لودر كاتربيلر بلقطات قريبة مهتزة</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -19360,18 +19542,22 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>equipment; earthworks</t>
-        </is>
-      </c>
-      <c r="G224" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H224" s="2" t="inlineStr"/>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="G224" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>Very shaky close-ups.</t>
+        </is>
+      </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 32.0 s · 30 fps · H264 · 4.1 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
+          <t>478×850 portrait · 20.7 s · 30 fps · H264 · 4.6 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: shaky handheld · view: ground · daylight</t>
         </is>
       </c>
       <c r="J224" s="3" t="inlineStr">
@@ -19385,14 +19571,14 @@
       <c r="N224" s="6" t="inlineStr"/>
       <c r="O224" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0030.mp4</t>
+          <t>VID-20260914-WA0024.mp4</t>
         </is>
       </c>
     </row>
     <row r="225" ht="88" customHeight="1">
       <c r="A225" s="2" t="inlineStr"/>
       <c r="B225" s="3" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
@@ -19401,7 +19587,7 @@
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>جريدر ومسّاح (نسخة معاد ضغطها من فيديو 006)</t>
+          <t>جريدر كاتربيلر يدور على رمال</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -19411,22 +19597,18 @@
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>earthworks; surveying</t>
-        </is>
-      </c>
-      <c r="G225" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H225" s="2" t="inlineStr">
-        <is>
-          <t>Re-encoded copy of video 006.</t>
-        </is>
-      </c>
+          <t>equipment; earthworks</t>
+        </is>
+      </c>
+      <c r="G225" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr"/>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>848×478 landscape · 14.5 s · 30 fps · H264 · 3.2 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static with zoom · view: ground · daylight</t>
+          <t>478×850 portrait · 14.6 s · 30 fps · H264 · 3.2 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
         </is>
       </c>
       <c r="J225" s="3" t="inlineStr">
@@ -19436,22 +19618,18 @@
       </c>
       <c r="K225" s="2" t="inlineStr"/>
       <c r="L225" s="2" t="inlineStr"/>
-      <c r="M225" s="2" t="inlineStr">
-        <is>
-          <t>video-006</t>
-        </is>
-      </c>
+      <c r="M225" s="2" t="inlineStr"/>
       <c r="N225" s="6" t="inlineStr"/>
       <c r="O225" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0031.mp4</t>
+          <t>VID-20260914-WA0025.mp4</t>
         </is>
       </c>
     </row>
     <row r="226" ht="88" customHeight="1">
       <c r="A226" s="2" t="inlineStr"/>
       <c r="B226" s="3" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
@@ -19460,17 +19638,17 @@
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>حماية ميول أسفل كوبري بألواح خرسانية</t>
+          <t>تسوية ساتر ترابي أحمر بالجريدر أثناء المشي</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Bridges &amp; axes — الكباري والمحاور</t>
+          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>concrete slopes; bridge</t>
+          <t>earthworks; equipment</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
@@ -19480,12 +19658,12 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>Only clip that shows work at a flyover.</t>
+          <t>Tilted at times.</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 25.3 s · 30 fps · H264 · 5.4 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
+          <t>478×850 portrait · 30.9 s · 30 fps · H264 · 4.0 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
         </is>
       </c>
       <c r="J226" s="3" t="inlineStr">
@@ -19499,14 +19677,14 @@
       <c r="N226" s="6" t="inlineStr"/>
       <c r="O226" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0032.mp4</t>
+          <t>VID-20260914-WA0026.mp4</t>
         </is>
       </c>
     </row>
     <row r="227" ht="88" customHeight="1">
       <c r="A227" s="2" t="inlineStr"/>
       <c r="B227" s="3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
@@ -19515,7 +19693,7 @@
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>داخل مبنى مصنع: شدات أعمدة وسقالات</t>
+          <t>هنجر معدني بسقالات وأعمدة</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -19525,7 +19703,7 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>building works; formwork</t>
+          <t>steel structure</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
@@ -19533,10 +19711,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>Similar subject to video 004.</t>
+        </is>
+      </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 34.4 s · 30 fps · H264 · 5.7 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
+          <t>474×850 portrait · 11.8 s · 30 fps · H264 · 1.9 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld pan · view: ground · daylight</t>
         </is>
       </c>
       <c r="J227" s="3" t="inlineStr">
@@ -19550,14 +19732,14 @@
       <c r="N227" s="6" t="inlineStr"/>
       <c r="O227" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0033.mp4</t>
+          <t>VID-20260914-WA0027.mp4</t>
         </is>
       </c>
     </row>
     <row r="228" ht="88" customHeight="1">
       <c r="A228" s="2" t="inlineStr"/>
       <c r="B228" s="3" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
@@ -19566,7 +19748,7 @@
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>ماكينة دهان خطوط طرق ترسم خطًا أصفر على الأسفلت مع عمال</t>
+          <t>لقطات سينمائية للودر كاتربيلر 966E</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -19576,7 +19758,7 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>road marking; workers</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
@@ -19586,37 +19768,33 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>Unique road-marking footage; faces partly visible — needs permission.</t>
+          <t>One out-of-focus section; likely raw footage for the company edit.</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 55.2 s · 30 fps · H264 · 7.2 MB · audio: aac mono · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
-        </is>
-      </c>
-      <c r="J228" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>848×478 landscape · 21.0 s · 30 fps · H264 · 4.7 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: stabilised, cinematic · view: ground · daylight</t>
+        </is>
+      </c>
+      <c r="J228" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K228" s="2" t="inlineStr"/>
-      <c r="L228" s="2" t="inlineStr">
-        <is>
-          <t>faces — publishing permission granted 2026-09-16</t>
-        </is>
-      </c>
+      <c r="L228" s="2" t="inlineStr"/>
       <c r="M228" s="2" t="inlineStr"/>
       <c r="N228" s="6" t="inlineStr"/>
       <c r="O228" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0036.mp4</t>
+          <t>VID-20260914-WA0028.mp4</t>
         </is>
       </c>
     </row>
     <row r="229" ht="88" customHeight="1">
       <c r="A229" s="2" t="inlineStr"/>
       <c r="B229" s="3" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
@@ -19625,37 +19803,33 @@
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>هنجر معدني ورجل يسير نحو الكاميرا</t>
+          <t>جريدر بزاوية منخفضة سينمائية</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>Brick factories — مصانع الطوب</t>
+          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>steel structure; people</t>
-        </is>
-      </c>
-      <c r="G229" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H229" s="2" t="inlineStr">
-        <is>
-          <t>A man walks into the lens with a clear face; shaky.</t>
-        </is>
-      </c>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="G229" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr"/>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 13.4 s · 30 fps · H264 · 2.0 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: shaky handheld · view: ground · daylight</t>
-        </is>
-      </c>
-      <c r="J229" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>848×478 landscape · 12.7 s · 30 fps · H264 · 2.8 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: stabilised, cinematic · view: ground · daylight</t>
+        </is>
+      </c>
+      <c r="J229" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K229" s="2" t="inlineStr"/>
@@ -19664,14 +19838,14 @@
       <c r="N229" s="6" t="inlineStr"/>
       <c r="O229" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0037.mp4</t>
+          <t>VID-20260914-WA0029.mp4</t>
         </is>
       </c>
     </row>
     <row r="230" ht="88" customHeight="1">
       <c r="A230" s="2" t="inlineStr"/>
       <c r="B230" s="3" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
@@ -19680,7 +19854,7 @@
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>لودر يدفع رملًا مع غبار</t>
+          <t>لودر يدفع رملًا على منحدر</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -19701,7 +19875,7 @@
       <c r="H230" s="2" t="inlineStr"/>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 14.0 s · 30 fps · H264 · 3.1 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
+          <t>478×850 portrait · 32.0 s · 30 fps · H264 · 4.1 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
         </is>
       </c>
       <c r="J230" s="3" t="inlineStr">
@@ -19715,14 +19889,14 @@
       <c r="N230" s="6" t="inlineStr"/>
       <c r="O230" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0038.mp4</t>
+          <t>VID-20260914-WA0030.mp4</t>
         </is>
       </c>
     </row>
     <row r="231" ht="88" customHeight="1">
       <c r="A231" s="2" t="inlineStr"/>
       <c r="B231" s="3" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
@@ -19731,7 +19905,7 @@
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>لودر يقترب عبر أرض ممهّدة</t>
+          <t>جريدر ومسّاح (نسخة معاد ضغطها من فيديو 006)</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -19741,18 +19915,22 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>equipment; earthworks</t>
-        </is>
-      </c>
-      <c r="G231" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H231" s="2" t="inlineStr"/>
+          <t>earthworks; surveying</t>
+        </is>
+      </c>
+      <c r="G231" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>Re-encoded copy of video 006.</t>
+        </is>
+      </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 10.9 s · 29 fps · H264 · 2.4 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static · view: ground · daylight</t>
+          <t>848×478 landscape · 14.5 s · 30 fps · H264 · 3.2 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static with zoom · view: ground · daylight</t>
         </is>
       </c>
       <c r="J231" s="3" t="inlineStr">
@@ -19762,18 +19940,22 @@
       </c>
       <c r="K231" s="2" t="inlineStr"/>
       <c r="L231" s="2" t="inlineStr"/>
-      <c r="M231" s="2" t="inlineStr"/>
+      <c r="M231" s="2" t="inlineStr">
+        <is>
+          <t>video-006</t>
+        </is>
+      </c>
       <c r="N231" s="6" t="inlineStr"/>
       <c r="O231" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0048.mp4</t>
+          <t>VID-20260914-WA0031.mp4</t>
         </is>
       </c>
     </row>
     <row r="232" ht="88" customHeight="1">
       <c r="A232" s="2" t="inlineStr"/>
       <c r="B232" s="3" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
@@ -19782,32 +19964,32 @@
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>مشي على حافة حفر مع ظل المصوّر</t>
+          <t>حماية ميول أسفل كوبري بألواح خرسانية</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
+          <t>Bridges &amp; axes — الكباري والمحاور</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>earthworks</t>
-        </is>
-      </c>
-      <c r="G232" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>concrete slopes; bridge</t>
+        </is>
+      </c>
+      <c r="G232" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>Shaky walk with the camera operator's shadow.</t>
+          <t>Only clip that shows work at a flyover.</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>474×850 portrait · 14.9 s · 30 fps · H264 · 1.6 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: shaky handheld · view: ground · daylight</t>
+          <t>478×850 portrait · 25.3 s · 30 fps · H264 · 5.4 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
         </is>
       </c>
       <c r="J232" s="3" t="inlineStr">
@@ -19821,14 +20003,14 @@
       <c r="N232" s="6" t="inlineStr"/>
       <c r="O232" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0049.mp4</t>
+          <t>VID-20260914-WA0032.mp4</t>
         </is>
       </c>
     </row>
     <row r="233" ht="88" customHeight="1">
       <c r="A233" s="2" t="inlineStr"/>
       <c r="B233" s="3" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
@@ -19837,7 +20019,7 @@
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>أقفاص حديد تسليح لأساسات داخل هنجر مع شخص وقدم المصوّر</t>
+          <t>داخل مبنى مصنع: شدات أعمدة وسقالات</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -19847,27 +20029,23 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>foundations; rebar; people</t>
-        </is>
-      </c>
-      <c r="G233" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H233" s="2" t="inlineStr">
-        <is>
-          <t>Clear face and the operator's foot in frame.</t>
-        </is>
-      </c>
+          <t>building works; formwork</t>
+        </is>
+      </c>
+      <c r="G233" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr"/>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 52.6 s · 30 fps · H264 · 7.2 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
-        </is>
-      </c>
-      <c r="J233" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>478×850 portrait · 34.4 s · 30 fps · H264 · 5.7 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
+        </is>
+      </c>
+      <c r="J233" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K233" s="2" t="inlineStr"/>
@@ -19876,14 +20054,14 @@
       <c r="N233" s="6" t="inlineStr"/>
       <c r="O233" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0050.mp4</t>
+          <t>VID-20260914-WA0033.mp4</t>
         </is>
       </c>
     </row>
     <row r="234" ht="88" customHeight="1">
       <c r="A234" s="2" t="inlineStr"/>
       <c r="B234" s="3" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
@@ -19892,7 +20070,7 @@
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>جريدر بلقطات سينمائية منخفضة</t>
+          <t>ماكينة دهان خطوط طرق ترسم خطًا أصفر على الأسفلت مع عمال</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -19902,7 +20080,7 @@
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>equipment</t>
+          <t>road marking; workers</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
@@ -19912,33 +20090,37 @@
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>Likely raw footage for the company edit.</t>
+          <t>Unique road-marking footage; faces partly visible — needs permission.</t>
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>848×478 landscape · 13.1 s · 30 fps · H264 · 2.9 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: stabilised, cinematic · view: ground · daylight</t>
-        </is>
-      </c>
-      <c r="J234" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>478×850 portrait · 55.2 s · 30 fps · H264 · 7.2 MB · audio: aac mono · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
+        </is>
+      </c>
+      <c r="J234" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K234" s="2" t="inlineStr"/>
-      <c r="L234" s="2" t="inlineStr"/>
+      <c r="L234" s="2" t="inlineStr">
+        <is>
+          <t>faces — publishing permission granted 2026-09-16</t>
+        </is>
+      </c>
       <c r="M234" s="2" t="inlineStr"/>
       <c r="N234" s="6" t="inlineStr"/>
       <c r="O234" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0051.mp4</t>
+          <t>VID-20260914-WA0036.mp4</t>
         </is>
       </c>
     </row>
     <row r="235" ht="88" customHeight="1">
       <c r="A235" s="2" t="inlineStr"/>
       <c r="B235" s="3" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
@@ -19947,33 +20129,37 @@
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>لودر يحمّل شاحنات بالرمل</t>
+          <t>هنجر معدني ورجل يسير نحو الكاميرا</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
+          <t>Brick factories — مصانع الطوب</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>equipment; trucks</t>
-        </is>
-      </c>
-      <c r="G235" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H235" s="2" t="inlineStr"/>
+          <t>steel structure; people</t>
+        </is>
+      </c>
+      <c r="G235" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>A man walks into the lens with a clear face; shaky.</t>
+        </is>
+      </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>474×850 portrait · 64.1 s · 30 fps · H264 · 11.3 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
-        </is>
-      </c>
-      <c r="J235" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>478×850 portrait · 13.4 s · 30 fps · H264 · 2.0 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: shaky handheld · view: ground · daylight</t>
+        </is>
+      </c>
+      <c r="J235" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K235" s="2" t="inlineStr"/>
@@ -19982,14 +20168,14 @@
       <c r="N235" s="6" t="inlineStr"/>
       <c r="O235" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0052.mp4</t>
+          <t>VID-20260914-WA0037.mp4</t>
         </is>
       </c>
     </row>
     <row r="236" ht="88" customHeight="1">
       <c r="A236" s="2" t="inlineStr"/>
       <c r="B236" s="3" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
@@ -19998,7 +20184,7 @@
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>هراس اهتزازي بلقطات سينمائية قريبة</t>
+          <t>لودر يدفع رملًا مع غبار</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -20008,7 +20194,7 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>compaction; equipment</t>
+          <t>equipment; earthworks</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -20019,7 +20205,7 @@
       <c r="H236" s="2" t="inlineStr"/>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>848×478 landscape · 49.9 s · 30 fps · H264 · 11.0 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: stabilised, cinematic · view: ground · daylight</t>
+          <t>478×850 portrait · 14.0 s · 30 fps · H264 · 3.1 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
         </is>
       </c>
       <c r="J236" s="3" t="inlineStr">
@@ -20033,14 +20219,14 @@
       <c r="N236" s="6" t="inlineStr"/>
       <c r="O236" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0053.mp4</t>
+          <t>VID-20260914-WA0038.mp4</t>
         </is>
       </c>
     </row>
     <row r="237" ht="88" customHeight="1">
       <c r="A237" s="2" t="inlineStr"/>
       <c r="B237" s="3" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
@@ -20049,7 +20235,7 @@
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>جريدر يقترب على طريق ترابي أحمر</t>
+          <t>لودر يقترب عبر أرض ممهّدة</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -20059,7 +20245,7 @@
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>equipment</t>
+          <t>equipment; earthworks</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
@@ -20070,7 +20256,7 @@
       <c r="H237" s="2" t="inlineStr"/>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>848×478 landscape · 13.7 s · 30 fps · H264 · 3.0 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static · view: ground · daylight</t>
+          <t>478×850 portrait · 10.9 s · 29 fps · H264 · 2.4 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static · view: ground · daylight</t>
         </is>
       </c>
       <c r="J237" s="3" t="inlineStr">
@@ -20084,14 +20270,14 @@
       <c r="N237" s="6" t="inlineStr"/>
       <c r="O237" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0054.mp4</t>
+          <t>VID-20260914-WA0048.mp4</t>
         </is>
       </c>
     </row>
     <row r="238" ht="88" customHeight="1">
       <c r="A238" s="2" t="inlineStr"/>
       <c r="B238" s="3" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
@@ -20100,7 +20286,7 @@
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>عمال يصبّون ألواح ميول خرسانية مع خلاطة وأبراج كهرباء</t>
+          <t>مشي على حافة حفر مع ظل المصوّر</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -20110,18 +20296,22 @@
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>concrete slopes; workers</t>
-        </is>
-      </c>
-      <c r="G238" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H238" s="2" t="inlineStr"/>
+          <t>earthworks</t>
+        </is>
+      </c>
+      <c r="G238" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>Shaky walk with the camera operator's shadow.</t>
+        </is>
+      </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>848×480 landscape · 69.1 s · 30 fps · H264 · 11.3 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld pan · view: ground · daylight</t>
+          <t>474×850 portrait · 14.9 s · 30 fps · H264 · 1.6 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: shaky handheld · view: ground · daylight</t>
         </is>
       </c>
       <c r="J238" s="3" t="inlineStr">
@@ -20135,14 +20325,14 @@
       <c r="N238" s="6" t="inlineStr"/>
       <c r="O238" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0055.mp4</t>
+          <t>VID-20260914-WA0049.mp4</t>
         </is>
       </c>
     </row>
     <row r="239" ht="88" customHeight="1">
       <c r="A239" s="2" t="inlineStr"/>
       <c r="B239" s="3" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
@@ -20151,17 +20341,17 @@
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>هراس وجريدرات (قريب جدًا من فيديو 013)</t>
+          <t>أقفاص حديد تسليح لأساسات داخل هنجر مع شخص وقدم المصوّر</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
+          <t>Brick factories — مصانع الطوب</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>earthworks; compaction</t>
+          <t>foundations; rebar; people</t>
         </is>
       </c>
       <c r="G239" s="7" t="inlineStr">
@@ -20171,37 +20361,33 @@
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>Near-duplicate of video 013.</t>
+          <t>Clear face and the operator's foot in frame.</t>
         </is>
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>476×848 portrait · 23.3 s · 30 fps · H264 · 4.6 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
-        </is>
-      </c>
-      <c r="J239" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>478×850 portrait · 52.6 s · 30 fps · H264 · 7.2 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld walk · view: ground · daylight</t>
+        </is>
+      </c>
+      <c r="J239" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K239" s="2" t="inlineStr"/>
       <c r="L239" s="2" t="inlineStr"/>
-      <c r="M239" s="2" t="inlineStr">
-        <is>
-          <t>video-013</t>
-        </is>
-      </c>
+      <c r="M239" s="2" t="inlineStr"/>
       <c r="N239" s="6" t="inlineStr"/>
       <c r="O239" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0056.mp4</t>
+          <t>VID-20260914-WA0050.mp4</t>
         </is>
       </c>
     </row>
     <row r="240" ht="88" customHeight="1">
       <c r="A240" s="2" t="inlineStr"/>
       <c r="B240" s="3" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
@@ -20210,7 +20396,7 @@
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>لودر وجريدر على رمال</t>
+          <t>جريدر بلقطات سينمائية منخفضة</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -20220,7 +20406,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>equipment; earthworks</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
@@ -20228,10 +20414,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>Likely raw footage for the company edit.</t>
+        </is>
+      </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>478×850 portrait · 8.5 s · 29 fps · H264 · 1.8 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
+          <t>848×478 landscape · 13.1 s · 30 fps · H264 · 2.9 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: stabilised, cinematic · view: ground · daylight</t>
         </is>
       </c>
       <c r="J240" s="3" t="inlineStr">
@@ -20245,14 +20435,14 @@
       <c r="N240" s="6" t="inlineStr"/>
       <c r="O240" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0058.mp4</t>
+          <t>VID-20260914-WA0051.mp4</t>
         </is>
       </c>
     </row>
     <row r="241" ht="88" customHeight="1">
       <c r="A241" s="2" t="inlineStr"/>
       <c r="B241" s="3" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
@@ -20261,7 +20451,7 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>تبطين ميول خرسانية بنقشة متعرجة على جسر طريق جبلي مع خلاطات وعمال</t>
+          <t>لودر يحمّل شاحنات بالرمل</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -20271,7 +20461,7 @@
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>concrete slopes; workers; equipment</t>
+          <t>equipment; trucks</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
@@ -20279,14 +20469,10 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H241" s="2" t="inlineStr">
-        <is>
-          <t>Strong subject; low resolution.</t>
-        </is>
-      </c>
+      <c r="H241" s="2" t="inlineStr"/>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>848×480 landscape · 51.5 s · 30 fps · H264 · 9.7 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld pan · view: ground · daylight</t>
+          <t>474×850 portrait · 64.1 s · 30 fps · H264 · 11.3 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
         </is>
       </c>
       <c r="J241" s="3" t="inlineStr">
@@ -20300,14 +20486,14 @@
       <c r="N241" s="6" t="inlineStr"/>
       <c r="O241" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0060.mp4</t>
+          <t>VID-20260914-WA0052.mp4</t>
         </is>
       </c>
     </row>
     <row r="242" ht="88" customHeight="1">
       <c r="A242" s="2" t="inlineStr"/>
       <c r="B242" s="3" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
@@ -20316,7 +20502,7 @@
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>نفس أعمال الميول الخرسانية بلقطة طويلة</t>
+          <t>هراس اهتزازي بلقطات سينمائية قريبة</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -20326,7 +20512,7 @@
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>concrete slopes; workers</t>
+          <t>compaction; equipment</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
@@ -20334,14 +20520,10 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H242" s="2" t="inlineStr">
-        <is>
-          <t>Long (3 min).</t>
-        </is>
-      </c>
+      <c r="H242" s="2" t="inlineStr"/>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>848×480 landscape · 178.3 s · 30 fps · H264 · 22.9 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld pan · view: ground · daylight</t>
+          <t>848×478 landscape · 49.9 s · 30 fps · H264 · 11.0 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: stabilised, cinematic · view: ground · daylight</t>
         </is>
       </c>
       <c r="J242" s="3" t="inlineStr">
@@ -20355,14 +20537,14 @@
       <c r="N242" s="6" t="inlineStr"/>
       <c r="O242" s="2" t="inlineStr">
         <is>
-          <t>VID-20260914-WA0062.mp4</t>
+          <t>VID-20260914-WA0053.mp4</t>
         </is>
       </c>
     </row>
     <row r="243" ht="88" customHeight="1">
       <c r="A243" s="2" t="inlineStr"/>
       <c r="B243" s="3" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
@@ -20371,7 +20553,7 @@
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>الفيديو المُجمَّع للشركة بجودة عالية: جريدرات ولوادر وتصوير جوي وشعار</t>
+          <t>جريدر يقترب على طريق ترابي أحمر</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -20381,22 +20563,18 @@
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>earthworks; equipment; aerial; brand</t>
-        </is>
-      </c>
-      <c r="G243" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H243" s="2" t="inlineStr">
-        <is>
-          <t>High-quality 1920×1080 50 fps master of the company edit (the site currently uses a 1920×864 copy): best source for a new hero cut and stills.</t>
-        </is>
-      </c>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr"/>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>1920×1080 landscape · 192.5 s · 50 fps · HEVC · 285.9 MB · audio: aac stereo · camera: stabilised, cinematic · view: ground + aerial (drone) · daylight</t>
+          <t>848×478 landscape · 13.7 s · 30 fps · H264 · 3.0 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: static · view: ground · daylight</t>
         </is>
       </c>
       <c r="J243" s="3" t="inlineStr">
@@ -20404,28 +20582,20 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K243" s="2" t="inlineStr">
-        <is>
-          <t>Company logo intro/outro</t>
-        </is>
-      </c>
-      <c r="L243" s="2" t="inlineStr">
-        <is>
-          <t>company-owned footage including the aerial shots, confirmed 2026-09-16</t>
-        </is>
-      </c>
+      <c r="K243" s="2" t="inlineStr"/>
+      <c r="L243" s="2" t="inlineStr"/>
       <c r="M243" s="2" t="inlineStr"/>
       <c r="N243" s="6" t="inlineStr"/>
       <c r="O243" s="2" t="inlineStr">
         <is>
-          <t>FINAL.mp4</t>
+          <t>VID-20260914-WA0054.mp4</t>
         </is>
       </c>
     </row>
     <row r="244" ht="88" customHeight="1">
       <c r="A244" s="2" t="inlineStr"/>
       <c r="B244" s="3" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
@@ -20434,7 +20604,7 @@
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>ريل رأسي بجودة عالية ينتهي بشعار الشركة</t>
+          <t>عمال يصبّون ألواح ميول خرسانية مع خلاطة وأبراج كهرباء</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -20444,22 +20614,18 @@
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>earthworks; equipment; brand</t>
-        </is>
-      </c>
-      <c r="G244" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H244" s="2" t="inlineStr">
-        <is>
-          <t>High-quality 1080×1920 50 fps vertical reel: ideal for a mobile showcase.</t>
-        </is>
-      </c>
+          <t>concrete slopes; workers</t>
+        </is>
+      </c>
+      <c r="G244" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr"/>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>1080×1920 portrait · 22.7 s · 50 fps · HEVC · 52.1 MB · audio: aac stereo · camera: stabilised, cinematic · view: ground · daylight</t>
+          <t>848×480 landscape · 69.1 s · 30 fps · H264 · 11.3 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld pan · view: ground · daylight</t>
         </is>
       </c>
       <c r="J244" s="3" t="inlineStr">
@@ -20467,22 +20633,360 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K244" s="2" t="inlineStr">
-        <is>
-          <t>Company logo end card</t>
-        </is>
-      </c>
+      <c r="K244" s="2" t="inlineStr"/>
       <c r="L244" s="2" t="inlineStr"/>
       <c r="M244" s="2" t="inlineStr"/>
       <c r="N244" s="6" t="inlineStr"/>
       <c r="O244" s="2" t="inlineStr">
         <is>
+          <t>VID-20260914-WA0055.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="88" customHeight="1">
+      <c r="A245" s="2" t="inlineStr"/>
+      <c r="B245" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="D245" s="4" t="inlineStr">
+        <is>
+          <t>هراس وجريدرات (قريب جدًا من فيديو 013)</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>earthworks; compaction</t>
+        </is>
+      </c>
+      <c r="G245" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>Near-duplicate of video 013.</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>476×848 portrait · 23.3 s · 30 fps · H264 · 4.6 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
+        </is>
+      </c>
+      <c r="J245" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K245" s="2" t="inlineStr"/>
+      <c r="L245" s="2" t="inlineStr"/>
+      <c r="M245" s="2" t="inlineStr">
+        <is>
+          <t>video-013</t>
+        </is>
+      </c>
+      <c r="N245" s="6" t="inlineStr"/>
+      <c r="O245" s="2" t="inlineStr">
+        <is>
+          <t>VID-20260914-WA0056.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="88" customHeight="1">
+      <c r="A246" s="2" t="inlineStr"/>
+      <c r="B246" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="D246" s="4" t="inlineStr">
+        <is>
+          <t>لودر وجريدر على رمال</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>equipment; earthworks</t>
+        </is>
+      </c>
+      <c r="G246" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr"/>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>478×850 portrait · 8.5 s · 29 fps · H264 · 1.8 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld · view: ground · daylight</t>
+        </is>
+      </c>
+      <c r="J246" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K246" s="2" t="inlineStr"/>
+      <c r="L246" s="2" t="inlineStr"/>
+      <c r="M246" s="2" t="inlineStr"/>
+      <c r="N246" s="6" t="inlineStr"/>
+      <c r="O246" s="2" t="inlineStr">
+        <is>
+          <t>VID-20260914-WA0058.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="88" customHeight="1">
+      <c r="A247" s="2" t="inlineStr"/>
+      <c r="B247" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="D247" s="4" t="inlineStr">
+        <is>
+          <t>تبطين ميول خرسانية بنقشة متعرجة على جسر طريق جبلي مع خلاطات وعمال</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>concrete slopes; workers; equipment</t>
+        </is>
+      </c>
+      <c r="G247" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>Strong subject; low resolution.</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>848×480 landscape · 51.5 s · 30 fps · H264 · 9.7 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld pan · view: ground · daylight</t>
+        </is>
+      </c>
+      <c r="J247" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K247" s="2" t="inlineStr"/>
+      <c r="L247" s="2" t="inlineStr"/>
+      <c r="M247" s="2" t="inlineStr"/>
+      <c r="N247" s="6" t="inlineStr"/>
+      <c r="O247" s="2" t="inlineStr">
+        <is>
+          <t>VID-20260914-WA0060.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="88" customHeight="1">
+      <c r="A248" s="2" t="inlineStr"/>
+      <c r="B248" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="inlineStr">
+        <is>
+          <t>نفس أعمال الميول الخرسانية بلقطة طويلة</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>concrete slopes; workers</t>
+        </is>
+      </c>
+      <c r="G248" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>Long (3 min).</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>848×480 landscape · 178.3 s · 30 fps · H264 · 22.9 MB · audio: aac stereo · WhatsApp-compressed, low resolution · camera: handheld pan · view: ground · daylight</t>
+        </is>
+      </c>
+      <c r="J248" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K248" s="2" t="inlineStr"/>
+      <c r="L248" s="2" t="inlineStr"/>
+      <c r="M248" s="2" t="inlineStr"/>
+      <c r="N248" s="6" t="inlineStr"/>
+      <c r="O248" s="2" t="inlineStr">
+        <is>
+          <t>VID-20260914-WA0062.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="88" customHeight="1">
+      <c r="A249" s="2" t="inlineStr"/>
+      <c r="B249" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="D249" s="4" t="inlineStr">
+        <is>
+          <t>الفيديو المُجمَّع للشركة بجودة عالية: جريدرات ولوادر وتصوير جوي وشعار</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>earthworks; equipment; aerial; brand</t>
+        </is>
+      </c>
+      <c r="G249" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>High-quality 1920×1080 50 fps master of the company edit (the site currently uses a 1920×864 copy): best source for a new hero cut and stills.</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080 landscape · 192.5 s · 50 fps · HEVC · 285.9 MB · audio: aac stereo · camera: stabilised, cinematic · view: ground + aerial (drone) · daylight</t>
+        </is>
+      </c>
+      <c r="J249" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K249" s="2" t="inlineStr">
+        <is>
+          <t>Company logo intro/outro</t>
+        </is>
+      </c>
+      <c r="L249" s="2" t="inlineStr">
+        <is>
+          <t>company-owned footage including the aerial shots, confirmed 2026-09-16</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="inlineStr"/>
+      <c r="N249" s="6" t="inlineStr"/>
+      <c r="O249" s="2" t="inlineStr">
+        <is>
+          <t>FINAL.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="88" customHeight="1">
+      <c r="A250" s="2" t="inlineStr"/>
+      <c r="B250" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="D250" s="4" t="inlineStr">
+        <is>
+          <t>ريل رأسي بجودة عالية ينتهي بشعار الشركة</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>Roads &amp; infrastructure — الطرق والبنية التحتية</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>earthworks; equipment; brand</t>
+        </is>
+      </c>
+      <c r="G250" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>High-quality 1080×1920 50 fps vertical reel: ideal for a mobile showcase.</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>1080×1920 portrait · 22.7 s · 50 fps · HEVC · 52.1 MB · audio: aac stereo · camera: stabilised, cinematic · view: ground · daylight</t>
+        </is>
+      </c>
+      <c r="J250" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K250" s="2" t="inlineStr">
+        <is>
+          <t>Company logo end card</t>
+        </is>
+      </c>
+      <c r="L250" s="2" t="inlineStr"/>
+      <c r="M250" s="2" t="inlineStr"/>
+      <c r="N250" s="6" t="inlineStr"/>
+      <c r="O250" s="2" t="inlineStr">
+        <is>
           <t>reel 1.mp4</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O244"/>
+  <autoFilter ref="A1:O250"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -20494,7 +20998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -20504,7 +21008,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>Media triage — client photos &amp; videos (batch 1)</t>
+          <t>Media triage — client photos &amp; videos (batches 1 and 2)</t>
         </is>
       </c>
       <c r="B1" s="11" t="inlineStr"/>
@@ -20517,7 +21021,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>Batch 1: 2026-09-15 · Batch 2: 2026-09-18</t>
         </is>
       </c>
     </row>
@@ -20529,169 +21033,181 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>incoming-photos&amp;videos/ (originals untouched; renamed copies in media-work/)</t>
+          <t>incoming-photos&amp;videos/ and incoming-photos&amp;videos/batch2/ (originals untouched; renamed copies in media-work/)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr"/>
-      <c r="B4" s="11" t="inlineStr"/>
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Batch 2</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Photos 197–202, sent by the client for project 30 (International Coastal Road Development); the Project # column is filled in for them. Batch 1 is still unattributed.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Photos (files)</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n">
-        <v>196</v>
-      </c>
+      <c r="A5" s="11" t="inlineStr"/>
+      <c r="B5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Photos (distinct)</t>
+          <t>Photos (files)</t>
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>115</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Exact duplicate photos</t>
+          <t>Photos (distinct)</t>
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>81</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Distinct photos rated A / B / C</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>7 / 49 / 59</t>
-        </is>
+          <t>Exact duplicate photos</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Videos</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>47</v>
+          <t>Distinct photos rated A / B / C</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>9 / 52 / 60</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Videos rated A / B / C</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>2 / 34 / 11</t>
-        </is>
+          <t>Videos</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Duplicate or re-encoded videos</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="n">
-        <v>4</v>
+          <t>Videos rated A / B / C</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>2 / 34 / 11</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
+          <t>Duplicate or re-encoded videos</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
           <t>Distinct items with faces visible</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr"/>
-      <c r="B13" s="11" t="inlineStr"/>
+      <c r="B13" s="11" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr"/>
+      <c r="B14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Rating legend</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Strong enough for a hero, section background or featured card</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Fine inside a project gallery or grid</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Don't use: blurry, tiny, timestamped, wrong content, duplicates, security-sensitive, or people who can't be cropped out</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr"/>
-      <c r="B18" s="11" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Likely section</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Guessed from visible content only. The client must confirm the project in the "Project #" column before any photo appears on a project card.</t>
-        </is>
-      </c>
+      <c r="A19" s="11" t="inlineStr"/>
+      <c r="B19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
+          <t>Likely section</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Guessed from visible content only. The client must confirm the project in the "Project #" column before any photo appears on a project card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
           <t>Project #</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Use the # column of projects-inventory.xlsx (also listed on the "Projects" sheet).</t>
         </is>
@@ -20708,7 +21224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -21153,6 +21669,66 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>مصنع الطوب في السياحية أكتوبر</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Brick Factory – Al-Seyahia, 6th of October</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>تطوير طريق الدولي الساحلي</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>International Coastal Road Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>رفع كفاءة طريق محلة دمنة – المنصورة</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Mahallet Damana – Mansoura Road Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>رفع كفاءة طريق فارسكور – شربين – دمياط</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Faraskur – Sherbin – Damietta Road Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
